--- a/AAII_Financials/Yearly/NOA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NOA_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>NOA</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41364</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>559500</v>
+        <v>707400</v>
       </c>
       <c r="E8" s="3">
-        <v>475600</v>
+        <v>568700</v>
       </c>
       <c r="F8" s="3">
-        <v>362400</v>
+        <v>483400</v>
       </c>
       <c r="G8" s="3">
-        <v>522800</v>
+        <v>368400</v>
       </c>
       <c r="H8" s="3">
-        <v>298100</v>
+        <v>531400</v>
       </c>
       <c r="I8" s="3">
-        <v>212700</v>
+        <v>303000</v>
       </c>
       <c r="J8" s="3">
+        <v>216200</v>
+      </c>
+      <c r="K8" s="3">
         <v>155000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>211200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>370400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>362200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>410000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>515300</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>485600</v>
+        <v>593400</v>
       </c>
       <c r="E9" s="3">
-        <v>418900</v>
+        <v>493600</v>
       </c>
       <c r="F9" s="3">
-        <v>313600</v>
+        <v>425800</v>
       </c>
       <c r="G9" s="3">
-        <v>452700</v>
+        <v>318800</v>
       </c>
       <c r="H9" s="3">
-        <v>247900</v>
+        <v>460100</v>
       </c>
       <c r="I9" s="3">
-        <v>183900</v>
+        <v>252000</v>
       </c>
       <c r="J9" s="3">
+        <v>186900</v>
+      </c>
+      <c r="K9" s="3">
         <v>131500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>187300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>330000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>327000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>384500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>490700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>73800</v>
+        <v>114000</v>
       </c>
       <c r="E10" s="3">
-        <v>56700</v>
+        <v>75000</v>
       </c>
       <c r="F10" s="3">
-        <v>48800</v>
+        <v>57600</v>
       </c>
       <c r="G10" s="3">
-        <v>70100</v>
+        <v>49600</v>
       </c>
       <c r="H10" s="3">
-        <v>50200</v>
+        <v>71200</v>
       </c>
       <c r="I10" s="3">
-        <v>28800</v>
+        <v>51000</v>
       </c>
       <c r="J10" s="3">
+        <v>29300</v>
+      </c>
+      <c r="K10" s="3">
         <v>23500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>40400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>35200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24600</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,51 +961,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>-9500</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
-        <v>-20400</v>
+        <v>-9600</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-20700</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>1300</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>5000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -999,39 +1021,42 @@
       <c r="E15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3">
         <v>400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3300</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>507700</v>
+      <c r="D17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E17" s="3">
-        <v>435500</v>
+        <v>516100</v>
       </c>
       <c r="F17" s="3">
-        <v>313600</v>
+        <v>442700</v>
       </c>
       <c r="G17" s="3">
-        <v>480000</v>
+        <v>318800</v>
       </c>
       <c r="H17" s="3">
-        <v>276300</v>
+        <v>487900</v>
       </c>
       <c r="I17" s="3">
-        <v>202900</v>
+        <v>280900</v>
       </c>
       <c r="J17" s="3">
+        <v>206300</v>
+      </c>
+      <c r="K17" s="3">
         <v>152100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>209500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>361300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>369200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>422000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>526600</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>51700</v>
+      <c r="D18" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E18" s="3">
-        <v>40100</v>
+        <v>52600</v>
       </c>
       <c r="F18" s="3">
-        <v>48800</v>
+        <v>40700</v>
       </c>
       <c r="G18" s="3">
-        <v>42700</v>
+        <v>49600</v>
       </c>
       <c r="H18" s="3">
-        <v>21800</v>
+        <v>43500</v>
       </c>
       <c r="I18" s="3">
-        <v>9700</v>
+        <v>22200</v>
       </c>
       <c r="J18" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K18" s="3">
         <v>2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11400</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>26600</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3">
-        <v>16800</v>
+        <v>27100</v>
       </c>
       <c r="F20" s="3">
-        <v>7900</v>
+        <v>17100</v>
       </c>
       <c r="G20" s="3">
-        <v>1900</v>
+        <v>8100</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
       </c>
       <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
         <v>1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-15900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-14000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>165600</v>
+      <c r="D21" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E21" s="3">
-        <v>135800</v>
+        <v>168200</v>
       </c>
       <c r="F21" s="3">
-        <v>122100</v>
+        <v>138000</v>
       </c>
       <c r="G21" s="3">
-        <v>119500</v>
+        <v>124000</v>
       </c>
       <c r="H21" s="3">
-        <v>64900</v>
+        <v>121400</v>
       </c>
       <c r="I21" s="3">
-        <v>43200</v>
+        <v>65900</v>
       </c>
       <c r="J21" s="3">
+        <v>43900</v>
+      </c>
+      <c r="K21" s="3">
         <v>35000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>32900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>45400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>28900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12400</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>17000</v>
+        <v>19400</v>
       </c>
       <c r="E22" s="3">
-        <v>12700</v>
+        <v>17300</v>
       </c>
       <c r="F22" s="3">
-        <v>12800</v>
+        <v>13000</v>
       </c>
       <c r="G22" s="3">
-        <v>15600</v>
+        <v>13000</v>
       </c>
       <c r="H22" s="3">
-        <v>6400</v>
+        <v>15900</v>
       </c>
       <c r="I22" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J22" s="3">
         <v>5200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>16900</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1200</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>61400</v>
+        <v>63500</v>
       </c>
       <c r="E23" s="3">
-        <v>44100</v>
+        <v>62400</v>
       </c>
       <c r="F23" s="3">
-        <v>44000</v>
+        <v>44900</v>
       </c>
       <c r="G23" s="3">
-        <v>29100</v>
+        <v>44700</v>
       </c>
       <c r="H23" s="3">
-        <v>15600</v>
+        <v>29600</v>
       </c>
       <c r="I23" s="3">
-        <v>4700</v>
+        <v>15800</v>
       </c>
       <c r="J23" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-26600</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>12400</v>
+        <v>16900</v>
       </c>
       <c r="E24" s="3">
-        <v>6800</v>
+        <v>12600</v>
       </c>
       <c r="F24" s="3">
-        <v>8200</v>
+        <v>6900</v>
       </c>
       <c r="G24" s="3">
+        <v>8300</v>
+      </c>
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="H24" s="3">
-        <v>4400</v>
-      </c>
       <c r="I24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-4700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-6700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-7100</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>49000</v>
+        <v>46700</v>
       </c>
       <c r="E26" s="3">
-        <v>37400</v>
+        <v>49800</v>
       </c>
       <c r="F26" s="3">
-        <v>35800</v>
+        <v>38000</v>
       </c>
       <c r="G26" s="3">
-        <v>27000</v>
+        <v>36400</v>
       </c>
       <c r="H26" s="3">
-        <v>11100</v>
+        <v>27400</v>
       </c>
       <c r="I26" s="3">
-        <v>3800</v>
+        <v>11300</v>
       </c>
       <c r="J26" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-19500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>49000</v>
+        <v>46700</v>
       </c>
       <c r="E27" s="3">
-        <v>37400</v>
+        <v>49800</v>
       </c>
       <c r="F27" s="3">
-        <v>35800</v>
+        <v>38000</v>
       </c>
       <c r="G27" s="3">
-        <v>26800</v>
+        <v>36400</v>
       </c>
       <c r="H27" s="3">
-        <v>11100</v>
+        <v>27300</v>
       </c>
       <c r="I27" s="3">
-        <v>3800</v>
+        <v>11300</v>
       </c>
       <c r="J27" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1555,20 +1615,23 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>67200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>20200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>3200</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-26600</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3">
-        <v>-16800</v>
+        <v>-27100</v>
       </c>
       <c r="F32" s="3">
-        <v>-7900</v>
+        <v>-17100</v>
       </c>
       <c r="G32" s="3">
-        <v>-1900</v>
+        <v>-8100</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>-2000</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
       </c>
       <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>15900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>14000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>49000</v>
+        <v>46700</v>
       </c>
       <c r="E33" s="3">
-        <v>37400</v>
+        <v>49800</v>
       </c>
       <c r="F33" s="3">
-        <v>35800</v>
+        <v>38000</v>
       </c>
       <c r="G33" s="3">
-        <v>26800</v>
+        <v>36400</v>
       </c>
       <c r="H33" s="3">
-        <v>11100</v>
+        <v>27300</v>
       </c>
       <c r="I33" s="3">
-        <v>3800</v>
+        <v>11300</v>
       </c>
       <c r="J33" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>53300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-16300</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>49000</v>
+        <v>46700</v>
       </c>
       <c r="E35" s="3">
-        <v>37400</v>
+        <v>49800</v>
       </c>
       <c r="F35" s="3">
-        <v>35800</v>
+        <v>38000</v>
       </c>
       <c r="G35" s="3">
-        <v>26800</v>
+        <v>36400</v>
       </c>
       <c r="H35" s="3">
-        <v>11100</v>
+        <v>27300</v>
       </c>
       <c r="I35" s="3">
-        <v>3800</v>
+        <v>11300</v>
       </c>
       <c r="J35" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>53300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-16300</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41364</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,50 +1987,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>50300</v>
+        <v>65500</v>
       </c>
       <c r="E41" s="3">
-        <v>12100</v>
+        <v>51100</v>
       </c>
       <c r="F41" s="3">
-        <v>31600</v>
+        <v>12300</v>
       </c>
       <c r="G41" s="3">
-        <v>4000</v>
+        <v>32100</v>
       </c>
       <c r="H41" s="3">
-        <v>14200</v>
+        <v>4100</v>
       </c>
       <c r="I41" s="3">
+        <v>14400</v>
+      </c>
+      <c r="J41" s="3">
         <v>6000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1100</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1983,202 +2072,217 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>1200</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>72400</v>
+        <v>110700</v>
       </c>
       <c r="E43" s="3">
-        <v>57100</v>
+        <v>73600</v>
       </c>
       <c r="F43" s="3">
-        <v>57900</v>
+        <v>58000</v>
       </c>
       <c r="G43" s="3">
-        <v>62500</v>
+        <v>58800</v>
       </c>
       <c r="H43" s="3">
-        <v>67700</v>
+        <v>63500</v>
       </c>
       <c r="I43" s="3">
-        <v>49700</v>
+        <v>68800</v>
       </c>
       <c r="J43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="K43" s="3">
         <v>40700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>31800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>138700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>78800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>117900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>231200</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>36300</v>
+        <v>48000</v>
       </c>
       <c r="E44" s="3">
-        <v>32400</v>
+        <v>36900</v>
       </c>
       <c r="F44" s="3">
-        <v>13900</v>
+        <v>32900</v>
       </c>
       <c r="G44" s="3">
-        <v>15700</v>
+        <v>14200</v>
       </c>
       <c r="H44" s="3">
-        <v>9700</v>
+        <v>16000</v>
       </c>
       <c r="I44" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J44" s="3">
         <v>3500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8500</v>
+        <v>6500</v>
       </c>
       <c r="E45" s="3">
-        <v>5400</v>
+        <v>8600</v>
       </c>
       <c r="F45" s="3">
-        <v>9800</v>
+        <v>5500</v>
       </c>
       <c r="G45" s="3">
-        <v>3400</v>
+        <v>9900</v>
       </c>
       <c r="H45" s="3">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="I45" s="3">
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J45" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>145800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9600</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>167500</v>
+        <v>218100</v>
       </c>
       <c r="E46" s="3">
-        <v>107000</v>
+        <v>170200</v>
       </c>
       <c r="F46" s="3">
-        <v>86700</v>
+        <v>108800</v>
       </c>
       <c r="G46" s="3">
-        <v>85600</v>
+        <v>88100</v>
       </c>
       <c r="H46" s="3">
-        <v>94300</v>
+        <v>87100</v>
       </c>
       <c r="I46" s="3">
-        <v>64600</v>
+        <v>95900</v>
       </c>
       <c r="J46" s="3">
+        <v>65700</v>
+      </c>
+      <c r="K46" s="3">
         <v>54500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>59400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>118000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>98400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>268500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>251200</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>56800</v>
+        <v>60400</v>
       </c>
       <c r="E47" s="3">
-        <v>40700</v>
+        <v>57700</v>
       </c>
       <c r="F47" s="3">
-        <v>33600</v>
+        <v>41400</v>
       </c>
       <c r="G47" s="3">
-        <v>31200</v>
+        <v>34200</v>
       </c>
       <c r="H47" s="3">
-        <v>10700</v>
+        <v>31700</v>
       </c>
       <c r="I47" s="3">
+        <v>10900</v>
+      </c>
+      <c r="J47" s="3">
         <v>300</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -2192,96 +2296,105 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>480200</v>
+        <v>854100</v>
       </c>
       <c r="E48" s="3">
-        <v>471600</v>
+        <v>488100</v>
       </c>
       <c r="F48" s="3">
-        <v>468200</v>
+        <v>479400</v>
       </c>
       <c r="G48" s="3">
-        <v>439400</v>
+        <v>476000</v>
       </c>
       <c r="H48" s="3">
-        <v>761400</v>
+        <v>446700</v>
       </c>
       <c r="I48" s="3">
-        <v>195200</v>
+        <v>774000</v>
       </c>
       <c r="J48" s="3">
+        <v>198400</v>
+      </c>
+      <c r="K48" s="3">
         <v>179300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>388600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>204800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>194000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>210200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>245000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="E49" s="3">
-        <v>3200</v>
+        <v>5400</v>
       </c>
       <c r="F49" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G49" s="3">
         <v>300</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="H49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H49" s="3">
-        <v>2100</v>
-      </c>
       <c r="I49" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J49" s="3">
         <v>1400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3400</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
         <v>6500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>35200</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2300</v>
+        <v>4600</v>
       </c>
       <c r="E52" s="3">
-        <v>9500</v>
+        <v>2400</v>
       </c>
       <c r="F52" s="3">
-        <v>21100</v>
+        <v>9600</v>
       </c>
       <c r="G52" s="3">
-        <v>20000</v>
+        <v>21500</v>
       </c>
       <c r="H52" s="3">
-        <v>24300</v>
+        <v>20300</v>
       </c>
       <c r="I52" s="3">
-        <v>18100</v>
+        <v>24700</v>
       </c>
       <c r="J52" s="3">
+        <v>18400</v>
+      </c>
+      <c r="K52" s="3">
         <v>19400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>32100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>50600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>46200</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>712100</v>
+        <v>1142800</v>
       </c>
       <c r="E54" s="3">
-        <v>632000</v>
+        <v>723900</v>
       </c>
       <c r="F54" s="3">
-        <v>610000</v>
+        <v>642400</v>
       </c>
       <c r="G54" s="3">
-        <v>576300</v>
+        <v>620100</v>
       </c>
       <c r="H54" s="3">
-        <v>501500</v>
+        <v>585800</v>
       </c>
       <c r="I54" s="3">
-        <v>278900</v>
+        <v>509800</v>
       </c>
       <c r="J54" s="3">
+        <v>283500</v>
+      </c>
+      <c r="K54" s="3">
         <v>254500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>270400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>358400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>343100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>496800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>576200</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,260 +2655,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>74600</v>
+        <v>108000</v>
       </c>
       <c r="E57" s="3">
-        <v>55400</v>
+        <v>75800</v>
       </c>
       <c r="F57" s="3">
-        <v>30100</v>
+        <v>56300</v>
       </c>
       <c r="G57" s="3">
-        <v>64100</v>
+        <v>30600</v>
       </c>
       <c r="H57" s="3">
-        <v>46100</v>
+        <v>65200</v>
       </c>
       <c r="I57" s="3">
-        <v>25600</v>
+        <v>46900</v>
       </c>
       <c r="J57" s="3">
+        <v>26000</v>
+      </c>
+      <c r="K57" s="3">
         <v>21500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>45600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>37300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>55500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>131500</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>30600</v>
+        <v>60100</v>
       </c>
       <c r="E58" s="3">
-        <v>32500</v>
+        <v>31100</v>
       </c>
       <c r="F58" s="3">
-        <v>31400</v>
+        <v>33100</v>
       </c>
       <c r="G58" s="3">
-        <v>34700</v>
+        <v>31900</v>
       </c>
       <c r="H58" s="3">
-        <v>45300</v>
+        <v>35300</v>
       </c>
       <c r="I58" s="3">
-        <v>21200</v>
+        <v>46000</v>
       </c>
       <c r="J58" s="3">
+        <v>21500</v>
+      </c>
+      <c r="K58" s="3">
         <v>23400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>22500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>16100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>22100</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>34700</v>
+        <v>71300</v>
       </c>
       <c r="E59" s="3">
-        <v>29100</v>
+        <v>35200</v>
       </c>
       <c r="F59" s="3">
-        <v>20400</v>
+        <v>29600</v>
       </c>
       <c r="G59" s="3">
-        <v>28300</v>
+        <v>20800</v>
       </c>
       <c r="H59" s="3">
-        <v>30800</v>
+        <v>28800</v>
       </c>
       <c r="I59" s="3">
-        <v>10700</v>
+        <v>31300</v>
       </c>
       <c r="J59" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K59" s="3">
         <v>8900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>23100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>72300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>53000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>139800</v>
+        <v>239400</v>
       </c>
       <c r="E60" s="3">
-        <v>117100</v>
+        <v>142100</v>
       </c>
       <c r="F60" s="3">
-        <v>79600</v>
+        <v>119000</v>
       </c>
       <c r="G60" s="3">
-        <v>114400</v>
+        <v>80900</v>
       </c>
       <c r="H60" s="3">
-        <v>108200</v>
+        <v>116200</v>
       </c>
       <c r="I60" s="3">
-        <v>56400</v>
+        <v>110000</v>
       </c>
       <c r="J60" s="3">
+        <v>57300</v>
+      </c>
+      <c r="K60" s="3">
         <v>53800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>46700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>74800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>72000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>143900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>195600</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>275100</v>
+        <v>451800</v>
       </c>
       <c r="E61" s="3">
-        <v>244100</v>
+        <v>279700</v>
       </c>
       <c r="F61" s="3">
-        <v>279200</v>
+        <v>248100</v>
       </c>
       <c r="G61" s="3">
-        <v>262100</v>
+        <v>283800</v>
       </c>
       <c r="H61" s="3">
-        <v>232800</v>
+        <v>266400</v>
       </c>
       <c r="I61" s="3">
-        <v>78400</v>
+        <v>236700</v>
       </c>
       <c r="J61" s="3">
+        <v>79700</v>
+      </c>
+      <c r="K61" s="3">
         <v>49900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>60400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>83300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>79500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>218800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>230500</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>74800</v>
+        <v>188100</v>
       </c>
       <c r="E62" s="3">
-        <v>68400</v>
+        <v>76000</v>
       </c>
       <c r="F62" s="3">
-        <v>70600</v>
+        <v>69500</v>
       </c>
       <c r="G62" s="3">
-        <v>68900</v>
+        <v>71800</v>
       </c>
       <c r="H62" s="3">
-        <v>51200</v>
+        <v>70000</v>
       </c>
       <c r="I62" s="3">
-        <v>38000</v>
+        <v>52000</v>
       </c>
       <c r="J62" s="3">
+        <v>38600</v>
+      </c>
+      <c r="K62" s="3">
         <v>35300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>34400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>51500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>43900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>37700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>51900</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>489700</v>
+        <v>879300</v>
       </c>
       <c r="E66" s="3">
-        <v>429500</v>
+        <v>497800</v>
       </c>
       <c r="F66" s="3">
-        <v>429400</v>
+        <v>436600</v>
       </c>
       <c r="G66" s="3">
-        <v>445300</v>
+        <v>436500</v>
       </c>
       <c r="H66" s="3">
-        <v>392600</v>
+        <v>452700</v>
       </c>
       <c r="I66" s="3">
-        <v>172800</v>
+        <v>399100</v>
       </c>
       <c r="J66" s="3">
+        <v>175700</v>
+      </c>
+      <c r="K66" s="3">
         <v>139000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>141600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>209600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>195400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>400500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>478000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>51300</v>
+        <v>90900</v>
       </c>
       <c r="E72" s="3">
-        <v>8600</v>
+        <v>52100</v>
       </c>
       <c r="F72" s="3">
-        <v>-25600</v>
+        <v>8800</v>
       </c>
       <c r="G72" s="3">
-        <v>-58100</v>
+        <v>-26000</v>
       </c>
       <c r="H72" s="3">
-        <v>-82800</v>
+        <v>-59000</v>
       </c>
       <c r="I72" s="3">
-        <v>-92400</v>
+        <v>-84200</v>
       </c>
       <c r="J72" s="3">
+        <v>-94000</v>
+      </c>
+      <c r="K72" s="3">
         <v>-94700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-95700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-92200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-87300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-141000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-142800</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>222400</v>
+        <v>263600</v>
       </c>
       <c r="E76" s="3">
-        <v>202400</v>
+        <v>226100</v>
       </c>
       <c r="F76" s="3">
-        <v>180600</v>
+        <v>205800</v>
       </c>
       <c r="G76" s="3">
-        <v>130900</v>
+        <v>183600</v>
       </c>
       <c r="H76" s="3">
-        <v>108800</v>
+        <v>133100</v>
       </c>
       <c r="I76" s="3">
-        <v>106100</v>
+        <v>110600</v>
       </c>
       <c r="J76" s="3">
+        <v>107800</v>
+      </c>
+      <c r="K76" s="3">
         <v>115600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>128900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>148800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>147700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>96300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>98200</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41364</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>49000</v>
+        <v>46700</v>
       </c>
       <c r="E81" s="3">
-        <v>37400</v>
+        <v>49800</v>
       </c>
       <c r="F81" s="3">
-        <v>35800</v>
+        <v>38000</v>
       </c>
       <c r="G81" s="3">
-        <v>26800</v>
+        <v>36400</v>
       </c>
       <c r="H81" s="3">
-        <v>11100</v>
+        <v>27300</v>
       </c>
       <c r="I81" s="3">
-        <v>3800</v>
+        <v>11300</v>
       </c>
       <c r="J81" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>53300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-16300</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>86700</v>
+        <v>97000</v>
       </c>
       <c r="E83" s="3">
-        <v>78500</v>
+        <v>88100</v>
       </c>
       <c r="F83" s="3">
-        <v>65000</v>
+        <v>79800</v>
       </c>
       <c r="G83" s="3">
-        <v>74400</v>
+        <v>66000</v>
       </c>
       <c r="H83" s="3">
-        <v>42700</v>
+        <v>75600</v>
       </c>
       <c r="I83" s="3">
-        <v>33200</v>
+        <v>43400</v>
       </c>
       <c r="J83" s="3">
+        <v>33700</v>
+      </c>
+      <c r="K83" s="3">
         <v>30900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>31600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>36600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>30600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>31200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>37600</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>123000</v>
+        <v>199800</v>
       </c>
       <c r="E89" s="3">
-        <v>120100</v>
+        <v>125000</v>
       </c>
       <c r="F89" s="3">
-        <v>106500</v>
+        <v>122100</v>
       </c>
       <c r="G89" s="3">
-        <v>114800</v>
+        <v>108300</v>
       </c>
       <c r="H89" s="3">
+        <v>116700</v>
+      </c>
+      <c r="I89" s="3">
+        <v>80800</v>
+      </c>
+      <c r="J89" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K89" s="3">
+        <v>29000</v>
+      </c>
+      <c r="L89" s="3">
+        <v>57900</v>
+      </c>
+      <c r="M89" s="3">
+        <v>32400</v>
+      </c>
+      <c r="N89" s="3">
         <v>79500</v>
       </c>
-      <c r="I89" s="3">
-        <v>36200</v>
-      </c>
-      <c r="J89" s="3">
-        <v>29000</v>
-      </c>
-      <c r="K89" s="3">
-        <v>57900</v>
-      </c>
-      <c r="L89" s="3">
-        <v>32400</v>
-      </c>
-      <c r="M89" s="3">
-        <v>79500</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>68600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>48600</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-81100</v>
+        <v>-149900</v>
       </c>
       <c r="E91" s="3">
-        <v>-81800</v>
+        <v>-82400</v>
       </c>
       <c r="F91" s="3">
-        <v>-85100</v>
+        <v>-83200</v>
       </c>
       <c r="G91" s="3">
-        <v>-114200</v>
+        <v>-86500</v>
       </c>
       <c r="H91" s="3">
-        <v>-58900</v>
+        <v>-116000</v>
       </c>
       <c r="I91" s="3">
-        <v>-39100</v>
+        <v>-59900</v>
       </c>
       <c r="J91" s="3">
+        <v>-39800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-19700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-24400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-24100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-24600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-40700</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-70900</v>
+        <v>-181000</v>
       </c>
       <c r="E94" s="3">
-        <v>-72200</v>
+        <v>-72000</v>
       </c>
       <c r="F94" s="3">
-        <v>-82000</v>
+        <v>-73400</v>
       </c>
       <c r="G94" s="3">
-        <v>-116800</v>
+        <v>-83400</v>
       </c>
       <c r="H94" s="3">
-        <v>-166200</v>
+        <v>-118700</v>
       </c>
       <c r="I94" s="3">
-        <v>-24400</v>
+        <v>-168900</v>
       </c>
       <c r="J94" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-7600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>119900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-34900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-49300</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,50 +4221,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E96" s="3">
         <v>-5700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="G96" s="3">
         <v>-3200</v>
       </c>
-      <c r="F96" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-1800</v>
-      </c>
       <c r="H96" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I96" s="3">
         <v>-1500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-1600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-1300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1700</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,65 +4398,71 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-14200</v>
+        <v>-5700</v>
       </c>
       <c r="E100" s="3">
-        <v>-67400</v>
+        <v>-14400</v>
       </c>
       <c r="F100" s="3">
+        <v>-68500</v>
+      </c>
+      <c r="G100" s="3">
         <v>3300</v>
       </c>
-      <c r="G100" s="3">
-        <v>-8200</v>
-      </c>
       <c r="H100" s="3">
-        <v>94900</v>
+        <v>-8300</v>
       </c>
       <c r="I100" s="3">
-        <v>-15700</v>
+        <v>96500</v>
       </c>
       <c r="J100" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-34900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-37900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-27100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-189700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-34400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>8</v>
@@ -4225,8 +4473,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4240,49 +4488,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>38200</v>
+        <v>13100</v>
       </c>
       <c r="E102" s="3">
-        <v>-19500</v>
+        <v>38800</v>
       </c>
       <c r="F102" s="3">
-        <v>27800</v>
+        <v>-19800</v>
       </c>
       <c r="G102" s="3">
-        <v>-10200</v>
+        <v>28300</v>
       </c>
       <c r="H102" s="3">
-        <v>8200</v>
+        <v>-10300</v>
       </c>
       <c r="I102" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J102" s="3">
         <v>-4000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>23600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>500</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NOA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NOA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>NOA</t>
   </si>
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>707400</v>
+        <v>697600</v>
       </c>
       <c r="E8" s="3">
-        <v>568700</v>
+        <v>560800</v>
       </c>
       <c r="F8" s="3">
-        <v>483400</v>
+        <v>476700</v>
       </c>
       <c r="G8" s="3">
-        <v>368400</v>
+        <v>363300</v>
       </c>
       <c r="H8" s="3">
-        <v>531400</v>
+        <v>524000</v>
       </c>
       <c r="I8" s="3">
-        <v>303000</v>
+        <v>298800</v>
       </c>
       <c r="J8" s="3">
-        <v>216200</v>
+        <v>213200</v>
       </c>
       <c r="K8" s="3">
         <v>155000</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>593400</v>
+        <v>585200</v>
       </c>
       <c r="E9" s="3">
-        <v>493600</v>
+        <v>486800</v>
       </c>
       <c r="F9" s="3">
-        <v>425800</v>
+        <v>419900</v>
       </c>
       <c r="G9" s="3">
-        <v>318800</v>
+        <v>314400</v>
       </c>
       <c r="H9" s="3">
-        <v>460100</v>
+        <v>453800</v>
       </c>
       <c r="I9" s="3">
-        <v>252000</v>
+        <v>248500</v>
       </c>
       <c r="J9" s="3">
-        <v>186900</v>
+        <v>184300</v>
       </c>
       <c r="K9" s="3">
         <v>131500</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>114000</v>
+        <v>112400</v>
       </c>
       <c r="E10" s="3">
-        <v>75000</v>
+        <v>74000</v>
       </c>
       <c r="F10" s="3">
-        <v>57600</v>
+        <v>56800</v>
       </c>
       <c r="G10" s="3">
-        <v>49600</v>
+        <v>48900</v>
       </c>
       <c r="H10" s="3">
-        <v>71200</v>
+        <v>70300</v>
       </c>
       <c r="I10" s="3">
-        <v>51000</v>
+        <v>50300</v>
       </c>
       <c r="J10" s="3">
-        <v>29300</v>
+        <v>28900</v>
       </c>
       <c r="K10" s="3">
         <v>23500</v>
@@ -977,10 +977,10 @@
         <v>8</v>
       </c>
       <c r="F14" s="3">
-        <v>-9600</v>
+        <v>-9500</v>
       </c>
       <c r="G14" s="3">
-        <v>-20700</v>
+        <v>-20400</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1076,26 +1076,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>627800</v>
       </c>
       <c r="E17" s="3">
-        <v>516100</v>
+        <v>509000</v>
       </c>
       <c r="F17" s="3">
-        <v>442700</v>
+        <v>436500</v>
       </c>
       <c r="G17" s="3">
-        <v>318800</v>
+        <v>314300</v>
       </c>
       <c r="H17" s="3">
-        <v>487900</v>
+        <v>481200</v>
       </c>
       <c r="I17" s="3">
-        <v>280900</v>
+        <v>277000</v>
       </c>
       <c r="J17" s="3">
-        <v>206300</v>
+        <v>203400</v>
       </c>
       <c r="K17" s="3">
         <v>152100</v>
@@ -1121,26 +1121,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>69800</v>
       </c>
       <c r="E18" s="3">
-        <v>52600</v>
+        <v>51900</v>
       </c>
       <c r="F18" s="3">
-        <v>40700</v>
+        <v>40200</v>
       </c>
       <c r="G18" s="3">
-        <v>49600</v>
+        <v>48900</v>
       </c>
       <c r="H18" s="3">
-        <v>43500</v>
+        <v>42800</v>
       </c>
       <c r="I18" s="3">
-        <v>22200</v>
+        <v>21800</v>
       </c>
       <c r="J18" s="3">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="K18" s="3">
         <v>2900</v>
@@ -1185,20 +1185,20 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>19000</v>
       </c>
       <c r="E20" s="3">
-        <v>27100</v>
+        <v>26700</v>
       </c>
       <c r="F20" s="3">
-        <v>17100</v>
+        <v>16800</v>
       </c>
       <c r="G20" s="3">
-        <v>8100</v>
+        <v>8000</v>
       </c>
       <c r="H20" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
@@ -1230,26 +1230,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>184200</v>
       </c>
       <c r="E21" s="3">
-        <v>168200</v>
+        <v>165300</v>
       </c>
       <c r="F21" s="3">
-        <v>138000</v>
+        <v>135500</v>
       </c>
       <c r="G21" s="3">
-        <v>124000</v>
+        <v>121800</v>
       </c>
       <c r="H21" s="3">
-        <v>121400</v>
+        <v>119100</v>
       </c>
       <c r="I21" s="3">
-        <v>65900</v>
+        <v>64700</v>
       </c>
       <c r="J21" s="3">
-        <v>43900</v>
+        <v>43100</v>
       </c>
       <c r="K21" s="3">
         <v>35000</v>
@@ -1276,22 +1276,22 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>19400</v>
+        <v>26100</v>
       </c>
       <c r="E22" s="3">
-        <v>17300</v>
+        <v>17000</v>
       </c>
       <c r="F22" s="3">
-        <v>13000</v>
+        <v>12800</v>
       </c>
       <c r="G22" s="3">
-        <v>13000</v>
+        <v>12800</v>
       </c>
       <c r="H22" s="3">
-        <v>15900</v>
+        <v>15600</v>
       </c>
       <c r="I22" s="3">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="J22" s="3">
         <v>5200</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>63500</v>
+        <v>62600</v>
       </c>
       <c r="E23" s="3">
-        <v>62400</v>
+        <v>61500</v>
       </c>
       <c r="F23" s="3">
-        <v>44900</v>
+        <v>44200</v>
       </c>
       <c r="G23" s="3">
-        <v>44700</v>
+        <v>44100</v>
       </c>
       <c r="H23" s="3">
-        <v>29600</v>
+        <v>29100</v>
       </c>
       <c r="I23" s="3">
-        <v>15800</v>
+        <v>15600</v>
       </c>
       <c r="J23" s="3">
-        <v>4800</v>
+        <v>4700</v>
       </c>
       <c r="K23" s="3">
         <v>-400</v>
@@ -1366,22 +1366,22 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>16900</v>
+        <v>16600</v>
       </c>
       <c r="E24" s="3">
-        <v>12600</v>
+        <v>12400</v>
       </c>
       <c r="F24" s="3">
-        <v>6900</v>
+        <v>6800</v>
       </c>
       <c r="G24" s="3">
-        <v>8300</v>
+        <v>8200</v>
       </c>
       <c r="H24" s="3">
         <v>2100</v>
       </c>
       <c r="I24" s="3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="J24" s="3">
         <v>900</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>46700</v>
+        <v>46000</v>
       </c>
       <c r="E26" s="3">
-        <v>49800</v>
+        <v>49100</v>
       </c>
       <c r="F26" s="3">
-        <v>38000</v>
+        <v>37500</v>
       </c>
       <c r="G26" s="3">
-        <v>36400</v>
+        <v>35900</v>
       </c>
       <c r="H26" s="3">
-        <v>27400</v>
+        <v>27100</v>
       </c>
       <c r="I26" s="3">
-        <v>11300</v>
+        <v>11200</v>
       </c>
       <c r="J26" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="K26" s="3">
         <v>-300</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>46700</v>
+        <v>46000</v>
       </c>
       <c r="E27" s="3">
-        <v>49800</v>
+        <v>49100</v>
       </c>
       <c r="F27" s="3">
-        <v>38000</v>
+        <v>37500</v>
       </c>
       <c r="G27" s="3">
-        <v>36400</v>
+        <v>35900</v>
       </c>
       <c r="H27" s="3">
-        <v>27300</v>
+        <v>26900</v>
       </c>
       <c r="I27" s="3">
-        <v>11300</v>
+        <v>11100</v>
       </c>
       <c r="J27" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="K27" s="3">
         <v>-300</v>
@@ -1725,20 +1725,20 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-19000</v>
       </c>
       <c r="E32" s="3">
-        <v>-27100</v>
+        <v>-26700</v>
       </c>
       <c r="F32" s="3">
-        <v>-17100</v>
+        <v>-16800</v>
       </c>
       <c r="G32" s="3">
-        <v>-8100</v>
+        <v>-8000</v>
       </c>
       <c r="H32" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>46700</v>
+        <v>46000</v>
       </c>
       <c r="E33" s="3">
-        <v>49800</v>
+        <v>49100</v>
       </c>
       <c r="F33" s="3">
-        <v>38000</v>
+        <v>37500</v>
       </c>
       <c r="G33" s="3">
-        <v>36400</v>
+        <v>35900</v>
       </c>
       <c r="H33" s="3">
-        <v>27300</v>
+        <v>26900</v>
       </c>
       <c r="I33" s="3">
-        <v>11300</v>
+        <v>11100</v>
       </c>
       <c r="J33" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="K33" s="3">
         <v>-300</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>46700</v>
+        <v>46000</v>
       </c>
       <c r="E35" s="3">
-        <v>49800</v>
+        <v>49100</v>
       </c>
       <c r="F35" s="3">
-        <v>38000</v>
+        <v>37500</v>
       </c>
       <c r="G35" s="3">
-        <v>36400</v>
+        <v>35900</v>
       </c>
       <c r="H35" s="3">
-        <v>27300</v>
+        <v>26900</v>
       </c>
       <c r="I35" s="3">
-        <v>11300</v>
+        <v>11100</v>
       </c>
       <c r="J35" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="K35" s="3">
         <v>-300</v>
@@ -1994,22 +1994,22 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>65500</v>
+        <v>64600</v>
       </c>
       <c r="E41" s="3">
-        <v>51100</v>
+        <v>50400</v>
       </c>
       <c r="F41" s="3">
-        <v>12300</v>
+        <v>12100</v>
       </c>
       <c r="G41" s="3">
-        <v>32100</v>
+        <v>31700</v>
       </c>
       <c r="H41" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="I41" s="3">
-        <v>14400</v>
+        <v>14200</v>
       </c>
       <c r="J41" s="3">
         <v>6000</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>110700</v>
+        <v>96800</v>
       </c>
       <c r="E43" s="3">
-        <v>73600</v>
+        <v>72600</v>
       </c>
       <c r="F43" s="3">
+        <v>57200</v>
+      </c>
+      <c r="G43" s="3">
         <v>58000</v>
       </c>
-      <c r="G43" s="3">
-        <v>58800</v>
-      </c>
       <c r="H43" s="3">
-        <v>63500</v>
+        <v>62600</v>
       </c>
       <c r="I43" s="3">
-        <v>68800</v>
+        <v>67800</v>
       </c>
       <c r="J43" s="3">
-        <v>50500</v>
+        <v>49800</v>
       </c>
       <c r="K43" s="3">
         <v>40700</v>
@@ -2129,22 +2129,22 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>48000</v>
+        <v>47300</v>
       </c>
       <c r="E44" s="3">
-        <v>36900</v>
+        <v>36400</v>
       </c>
       <c r="F44" s="3">
-        <v>32900</v>
+        <v>32500</v>
       </c>
       <c r="G44" s="3">
-        <v>14200</v>
+        <v>14000</v>
       </c>
       <c r="H44" s="3">
-        <v>16000</v>
+        <v>15800</v>
       </c>
       <c r="I44" s="3">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="J44" s="3">
         <v>3500</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="E45" s="3">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="F45" s="3">
         <v>5500</v>
       </c>
       <c r="G45" s="3">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="H45" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="I45" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="J45" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="K45" s="3">
         <v>1300</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>218100</v>
+        <v>215100</v>
       </c>
       <c r="E46" s="3">
-        <v>170200</v>
+        <v>167900</v>
       </c>
       <c r="F46" s="3">
-        <v>108800</v>
+        <v>107300</v>
       </c>
       <c r="G46" s="3">
-        <v>88100</v>
+        <v>86900</v>
       </c>
       <c r="H46" s="3">
-        <v>87100</v>
+        <v>85800</v>
       </c>
       <c r="I46" s="3">
-        <v>95900</v>
+        <v>94500</v>
       </c>
       <c r="J46" s="3">
-        <v>65700</v>
+        <v>64800</v>
       </c>
       <c r="K46" s="3">
         <v>54500</v>
@@ -2264,22 +2264,22 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>60400</v>
+        <v>59600</v>
       </c>
       <c r="E47" s="3">
-        <v>57700</v>
+        <v>56900</v>
       </c>
       <c r="F47" s="3">
-        <v>41400</v>
+        <v>40800</v>
       </c>
       <c r="G47" s="3">
-        <v>34200</v>
+        <v>33700</v>
       </c>
       <c r="H47" s="3">
-        <v>31700</v>
+        <v>31300</v>
       </c>
       <c r="I47" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="J47" s="3">
         <v>300</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>854100</v>
+        <v>842200</v>
       </c>
       <c r="E48" s="3">
-        <v>488100</v>
+        <v>482000</v>
       </c>
       <c r="F48" s="3">
-        <v>479400</v>
+        <v>477900</v>
       </c>
       <c r="G48" s="3">
-        <v>476000</v>
+        <v>474000</v>
       </c>
       <c r="H48" s="3">
-        <v>446700</v>
+        <v>444200</v>
       </c>
       <c r="I48" s="3">
-        <v>774000</v>
+        <v>769800</v>
       </c>
       <c r="J48" s="3">
-        <v>198400</v>
+        <v>203100</v>
       </c>
       <c r="K48" s="3">
         <v>179300</v>
@@ -2357,10 +2357,10 @@
         <v>5500</v>
       </c>
       <c r="E49" s="3">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="F49" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="G49" s="3">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>8</v>
       </c>
       <c r="I49" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="J49" s="3">
         <v>1400</v>
@@ -2492,22 +2492,22 @@
         <v>4600</v>
       </c>
       <c r="E52" s="3">
-        <v>2400</v>
+        <v>1700</v>
       </c>
       <c r="F52" s="3">
-        <v>9600</v>
+        <v>4400</v>
       </c>
       <c r="G52" s="3">
-        <v>21500</v>
+        <v>16600</v>
       </c>
       <c r="H52" s="3">
-        <v>20300</v>
+        <v>16300</v>
       </c>
       <c r="I52" s="3">
-        <v>24700</v>
+        <v>17900</v>
       </c>
       <c r="J52" s="3">
-        <v>18400</v>
+        <v>10800</v>
       </c>
       <c r="K52" s="3">
         <v>19400</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1142800</v>
+        <v>1127000</v>
       </c>
       <c r="E54" s="3">
-        <v>723900</v>
+        <v>713800</v>
       </c>
       <c r="F54" s="3">
-        <v>642400</v>
+        <v>633500</v>
       </c>
       <c r="G54" s="3">
-        <v>620100</v>
+        <v>611500</v>
       </c>
       <c r="H54" s="3">
-        <v>585800</v>
+        <v>577700</v>
       </c>
       <c r="I54" s="3">
-        <v>509800</v>
+        <v>502700</v>
       </c>
       <c r="J54" s="3">
-        <v>283500</v>
+        <v>279600</v>
       </c>
       <c r="K54" s="3">
         <v>254500</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>108000</v>
+        <v>106500</v>
       </c>
       <c r="E57" s="3">
-        <v>75800</v>
+        <v>74700</v>
       </c>
       <c r="F57" s="3">
-        <v>56300</v>
+        <v>55600</v>
       </c>
       <c r="G57" s="3">
-        <v>30600</v>
+        <v>30200</v>
       </c>
       <c r="H57" s="3">
-        <v>65200</v>
+        <v>64300</v>
       </c>
       <c r="I57" s="3">
-        <v>46900</v>
+        <v>46200</v>
       </c>
       <c r="J57" s="3">
-        <v>26000</v>
+        <v>25600</v>
       </c>
       <c r="K57" s="3">
         <v>21500</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>60100</v>
+        <v>59300</v>
       </c>
       <c r="E58" s="3">
-        <v>31100</v>
+        <v>30700</v>
       </c>
       <c r="F58" s="3">
-        <v>33100</v>
+        <v>32600</v>
       </c>
       <c r="G58" s="3">
-        <v>31900</v>
+        <v>31500</v>
       </c>
       <c r="H58" s="3">
-        <v>35300</v>
+        <v>34800</v>
       </c>
       <c r="I58" s="3">
-        <v>46000</v>
+        <v>45400</v>
       </c>
       <c r="J58" s="3">
-        <v>21500</v>
+        <v>21200</v>
       </c>
       <c r="K58" s="3">
         <v>23400</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>71300</v>
+        <v>70300</v>
       </c>
       <c r="E59" s="3">
-        <v>35200</v>
+        <v>34700</v>
       </c>
       <c r="F59" s="3">
-        <v>29600</v>
+        <v>29200</v>
       </c>
       <c r="G59" s="3">
-        <v>20800</v>
+        <v>20500</v>
       </c>
       <c r="H59" s="3">
-        <v>28800</v>
+        <v>28400</v>
       </c>
       <c r="I59" s="3">
-        <v>31300</v>
+        <v>30900</v>
       </c>
       <c r="J59" s="3">
-        <v>10900</v>
+        <v>10700</v>
       </c>
       <c r="K59" s="3">
         <v>8900</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>239400</v>
+        <v>236100</v>
       </c>
       <c r="E60" s="3">
-        <v>142100</v>
+        <v>140100</v>
       </c>
       <c r="F60" s="3">
-        <v>119000</v>
+        <v>117400</v>
       </c>
       <c r="G60" s="3">
-        <v>80900</v>
+        <v>79800</v>
       </c>
       <c r="H60" s="3">
-        <v>116200</v>
+        <v>114600</v>
       </c>
       <c r="I60" s="3">
-        <v>110000</v>
+        <v>108500</v>
       </c>
       <c r="J60" s="3">
-        <v>57300</v>
+        <v>56500</v>
       </c>
       <c r="K60" s="3">
         <v>53800</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>451800</v>
+        <v>445500</v>
       </c>
       <c r="E61" s="3">
-        <v>279700</v>
+        <v>275800</v>
       </c>
       <c r="F61" s="3">
-        <v>248100</v>
+        <v>244700</v>
       </c>
       <c r="G61" s="3">
-        <v>283800</v>
+        <v>279800</v>
       </c>
       <c r="H61" s="3">
-        <v>266400</v>
+        <v>262700</v>
       </c>
       <c r="I61" s="3">
-        <v>236700</v>
+        <v>233400</v>
       </c>
       <c r="J61" s="3">
-        <v>79700</v>
+        <v>78600</v>
       </c>
       <c r="K61" s="3">
         <v>49900</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>188100</v>
+        <v>185500</v>
       </c>
       <c r="E62" s="3">
-        <v>76000</v>
+        <v>74900</v>
       </c>
       <c r="F62" s="3">
-        <v>69500</v>
+        <v>68500</v>
       </c>
       <c r="G62" s="3">
-        <v>71800</v>
+        <v>70800</v>
       </c>
       <c r="H62" s="3">
-        <v>70000</v>
+        <v>69000</v>
       </c>
       <c r="I62" s="3">
-        <v>52000</v>
+        <v>51300</v>
       </c>
       <c r="J62" s="3">
-        <v>38600</v>
+        <v>38100</v>
       </c>
       <c r="K62" s="3">
         <v>35300</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>879300</v>
+        <v>867100</v>
       </c>
       <c r="E66" s="3">
-        <v>497800</v>
+        <v>490900</v>
       </c>
       <c r="F66" s="3">
-        <v>436600</v>
+        <v>430600</v>
       </c>
       <c r="G66" s="3">
-        <v>436500</v>
+        <v>430400</v>
       </c>
       <c r="H66" s="3">
-        <v>452700</v>
+        <v>446400</v>
       </c>
       <c r="I66" s="3">
-        <v>399100</v>
+        <v>393600</v>
       </c>
       <c r="J66" s="3">
-        <v>175700</v>
+        <v>173200</v>
       </c>
       <c r="K66" s="3">
         <v>139000</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>90900</v>
+        <v>89700</v>
       </c>
       <c r="E72" s="3">
-        <v>52100</v>
+        <v>51400</v>
       </c>
       <c r="F72" s="3">
-        <v>8800</v>
+        <v>8600</v>
       </c>
       <c r="G72" s="3">
-        <v>-26000</v>
+        <v>-25600</v>
       </c>
       <c r="H72" s="3">
-        <v>-59000</v>
+        <v>-58200</v>
       </c>
       <c r="I72" s="3">
-        <v>-84200</v>
+        <v>-83000</v>
       </c>
       <c r="J72" s="3">
-        <v>-94000</v>
+        <v>-92700</v>
       </c>
       <c r="K72" s="3">
         <v>-94700</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>263600</v>
+        <v>259900</v>
       </c>
       <c r="E76" s="3">
-        <v>226100</v>
+        <v>222900</v>
       </c>
       <c r="F76" s="3">
-        <v>205800</v>
+        <v>202900</v>
       </c>
       <c r="G76" s="3">
-        <v>183600</v>
+        <v>181100</v>
       </c>
       <c r="H76" s="3">
-        <v>133100</v>
+        <v>131300</v>
       </c>
       <c r="I76" s="3">
-        <v>110600</v>
+        <v>109100</v>
       </c>
       <c r="J76" s="3">
-        <v>107800</v>
+        <v>106300</v>
       </c>
       <c r="K76" s="3">
         <v>115600</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>46700</v>
+        <v>46000</v>
       </c>
       <c r="E81" s="3">
-        <v>49800</v>
+        <v>49100</v>
       </c>
       <c r="F81" s="3">
-        <v>38000</v>
+        <v>37500</v>
       </c>
       <c r="G81" s="3">
-        <v>36400</v>
+        <v>35900</v>
       </c>
       <c r="H81" s="3">
-        <v>27300</v>
+        <v>26900</v>
       </c>
       <c r="I81" s="3">
-        <v>11300</v>
+        <v>11100</v>
       </c>
       <c r="J81" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="K81" s="3">
         <v>-300</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>97000</v>
+        <v>95700</v>
       </c>
       <c r="E83" s="3">
-        <v>88100</v>
+        <v>86900</v>
       </c>
       <c r="F83" s="3">
-        <v>79800</v>
+        <v>78700</v>
       </c>
       <c r="G83" s="3">
-        <v>66000</v>
+        <v>65100</v>
       </c>
       <c r="H83" s="3">
-        <v>75600</v>
+        <v>74500</v>
       </c>
       <c r="I83" s="3">
-        <v>43400</v>
+        <v>42800</v>
       </c>
       <c r="J83" s="3">
-        <v>33700</v>
+        <v>33300</v>
       </c>
       <c r="K83" s="3">
         <v>30900</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>199800</v>
+        <v>197100</v>
       </c>
       <c r="E89" s="3">
-        <v>125000</v>
+        <v>123300</v>
       </c>
       <c r="F89" s="3">
-        <v>122100</v>
+        <v>120400</v>
       </c>
       <c r="G89" s="3">
-        <v>108300</v>
+        <v>106800</v>
       </c>
       <c r="H89" s="3">
-        <v>116700</v>
+        <v>115100</v>
       </c>
       <c r="I89" s="3">
-        <v>80800</v>
+        <v>79700</v>
       </c>
       <c r="J89" s="3">
-        <v>36800</v>
+        <v>36300</v>
       </c>
       <c r="K89" s="3">
         <v>29000</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-149900</v>
+        <v>-147800</v>
       </c>
       <c r="E91" s="3">
-        <v>-82400</v>
+        <v>-81300</v>
       </c>
       <c r="F91" s="3">
-        <v>-83200</v>
+        <v>-82000</v>
       </c>
       <c r="G91" s="3">
-        <v>-86500</v>
+        <v>-85300</v>
       </c>
       <c r="H91" s="3">
-        <v>-116000</v>
+        <v>-114400</v>
       </c>
       <c r="I91" s="3">
-        <v>-59900</v>
+        <v>-59100</v>
       </c>
       <c r="J91" s="3">
-        <v>-39800</v>
+        <v>-39200</v>
       </c>
       <c r="K91" s="3">
         <v>-19700</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-181000</v>
+        <v>-178500</v>
       </c>
       <c r="E94" s="3">
-        <v>-72000</v>
+        <v>-71000</v>
       </c>
       <c r="F94" s="3">
-        <v>-73400</v>
+        <v>-72300</v>
       </c>
       <c r="G94" s="3">
-        <v>-83400</v>
+        <v>-82200</v>
       </c>
       <c r="H94" s="3">
-        <v>-118700</v>
+        <v>-117100</v>
       </c>
       <c r="I94" s="3">
-        <v>-168900</v>
+        <v>-166600</v>
       </c>
       <c r="J94" s="3">
-        <v>-24800</v>
+        <v>-24500</v>
       </c>
       <c r="K94" s="3">
         <v>-7600</v>
@@ -4228,19 +4228,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-7400</v>
+        <v>-7300</v>
       </c>
       <c r="E96" s="3">
         <v>-5700</v>
       </c>
       <c r="F96" s="3">
-        <v>-3300</v>
+        <v>-3200</v>
       </c>
       <c r="G96" s="3">
         <v>-3200</v>
       </c>
       <c r="H96" s="3">
-        <v>-1900</v>
+        <v>-1800</v>
       </c>
       <c r="I96" s="3">
         <v>-1500</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-5700</v>
+        <v>-5600</v>
       </c>
       <c r="E100" s="3">
-        <v>-14400</v>
+        <v>-14200</v>
       </c>
       <c r="F100" s="3">
-        <v>-68500</v>
+        <v>-67600</v>
       </c>
       <c r="G100" s="3">
         <v>3300</v>
       </c>
       <c r="H100" s="3">
-        <v>-8300</v>
+        <v>-8200</v>
       </c>
       <c r="I100" s="3">
-        <v>96500</v>
+        <v>95200</v>
       </c>
       <c r="J100" s="3">
-        <v>-16000</v>
+        <v>-15800</v>
       </c>
       <c r="K100" s="3">
         <v>-34900</v>
@@ -4453,7 +4453,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="E101" s="3">
         <v>200</v>
@@ -4498,22 +4498,22 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>13100</v>
+        <v>14200</v>
       </c>
       <c r="E102" s="3">
-        <v>38800</v>
+        <v>38300</v>
       </c>
       <c r="F102" s="3">
-        <v>-19800</v>
+        <v>-19600</v>
       </c>
       <c r="G102" s="3">
-        <v>28300</v>
+        <v>27900</v>
       </c>
       <c r="H102" s="3">
-        <v>-10300</v>
+        <v>-10200</v>
       </c>
       <c r="I102" s="3">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="J102" s="3">
         <v>-4000</v>

--- a/AAII_Financials/Yearly/NOA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NOA_YR_FIN.xlsx
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>697600</v>
+        <v>704600</v>
       </c>
       <c r="E8" s="3">
-        <v>560800</v>
+        <v>566500</v>
       </c>
       <c r="F8" s="3">
-        <v>476700</v>
+        <v>481500</v>
       </c>
       <c r="G8" s="3">
-        <v>363300</v>
+        <v>366900</v>
       </c>
       <c r="H8" s="3">
-        <v>524000</v>
+        <v>529300</v>
       </c>
       <c r="I8" s="3">
-        <v>298800</v>
+        <v>301900</v>
       </c>
       <c r="J8" s="3">
-        <v>213200</v>
+        <v>215400</v>
       </c>
       <c r="K8" s="3">
         <v>155000</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>585200</v>
+        <v>591100</v>
       </c>
       <c r="E9" s="3">
-        <v>486800</v>
+        <v>491700</v>
       </c>
       <c r="F9" s="3">
-        <v>419900</v>
+        <v>424200</v>
       </c>
       <c r="G9" s="3">
-        <v>314400</v>
+        <v>317600</v>
       </c>
       <c r="H9" s="3">
-        <v>453800</v>
+        <v>458300</v>
       </c>
       <c r="I9" s="3">
-        <v>248500</v>
+        <v>251000</v>
       </c>
       <c r="J9" s="3">
-        <v>184300</v>
+        <v>186200</v>
       </c>
       <c r="K9" s="3">
         <v>131500</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>112400</v>
+        <v>113500</v>
       </c>
       <c r="E10" s="3">
-        <v>74000</v>
+        <v>74800</v>
       </c>
       <c r="F10" s="3">
-        <v>56800</v>
+        <v>57400</v>
       </c>
       <c r="G10" s="3">
-        <v>48900</v>
+        <v>49400</v>
       </c>
       <c r="H10" s="3">
-        <v>70300</v>
+        <v>71000</v>
       </c>
       <c r="I10" s="3">
-        <v>50300</v>
+        <v>50800</v>
       </c>
       <c r="J10" s="3">
-        <v>28900</v>
+        <v>29200</v>
       </c>
       <c r="K10" s="3">
         <v>23500</v>
@@ -977,10 +977,10 @@
         <v>8</v>
       </c>
       <c r="F14" s="3">
-        <v>-9500</v>
+        <v>-9600</v>
       </c>
       <c r="G14" s="3">
-        <v>-20400</v>
+        <v>-20600</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>627800</v>
+        <v>634200</v>
       </c>
       <c r="E17" s="3">
-        <v>509000</v>
+        <v>514100</v>
       </c>
       <c r="F17" s="3">
-        <v>436500</v>
+        <v>440900</v>
       </c>
       <c r="G17" s="3">
-        <v>314300</v>
+        <v>317500</v>
       </c>
       <c r="H17" s="3">
-        <v>481200</v>
+        <v>486000</v>
       </c>
       <c r="I17" s="3">
-        <v>277000</v>
+        <v>279800</v>
       </c>
       <c r="J17" s="3">
-        <v>203400</v>
+        <v>205500</v>
       </c>
       <c r="K17" s="3">
         <v>152100</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>69800</v>
+        <v>70500</v>
       </c>
       <c r="E18" s="3">
-        <v>51900</v>
+        <v>52400</v>
       </c>
       <c r="F18" s="3">
-        <v>40200</v>
+        <v>40600</v>
       </c>
       <c r="G18" s="3">
-        <v>48900</v>
+        <v>49400</v>
       </c>
       <c r="H18" s="3">
-        <v>42800</v>
+        <v>43300</v>
       </c>
       <c r="I18" s="3">
-        <v>21800</v>
+        <v>22100</v>
       </c>
       <c r="J18" s="3">
-        <v>9800</v>
+        <v>9900</v>
       </c>
       <c r="K18" s="3">
         <v>2900</v>
@@ -1186,19 +1186,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>19000</v>
+        <v>19200</v>
       </c>
       <c r="E20" s="3">
-        <v>26700</v>
+        <v>27000</v>
       </c>
       <c r="F20" s="3">
-        <v>16800</v>
+        <v>17000</v>
       </c>
       <c r="G20" s="3">
         <v>8000</v>
       </c>
       <c r="H20" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>184200</v>
+        <v>186300</v>
       </c>
       <c r="E21" s="3">
-        <v>165300</v>
+        <v>167200</v>
       </c>
       <c r="F21" s="3">
-        <v>135500</v>
+        <v>137100</v>
       </c>
       <c r="G21" s="3">
-        <v>121800</v>
+        <v>123300</v>
       </c>
       <c r="H21" s="3">
-        <v>119100</v>
+        <v>120600</v>
       </c>
       <c r="I21" s="3">
-        <v>64700</v>
+        <v>65500</v>
       </c>
       <c r="J21" s="3">
-        <v>43100</v>
+        <v>43600</v>
       </c>
       <c r="K21" s="3">
         <v>35000</v>
@@ -1276,19 +1276,19 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>26100</v>
+        <v>26300</v>
       </c>
       <c r="E22" s="3">
-        <v>17000</v>
+        <v>17200</v>
       </c>
       <c r="F22" s="3">
-        <v>12800</v>
+        <v>12900</v>
       </c>
       <c r="G22" s="3">
-        <v>12800</v>
+        <v>12900</v>
       </c>
       <c r="H22" s="3">
-        <v>15600</v>
+        <v>15800</v>
       </c>
       <c r="I22" s="3">
         <v>6400</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>62600</v>
+        <v>63300</v>
       </c>
       <c r="E23" s="3">
-        <v>61500</v>
+        <v>62200</v>
       </c>
       <c r="F23" s="3">
-        <v>44200</v>
+        <v>44700</v>
       </c>
       <c r="G23" s="3">
-        <v>44100</v>
+        <v>44500</v>
       </c>
       <c r="H23" s="3">
-        <v>29100</v>
+        <v>29400</v>
       </c>
       <c r="I23" s="3">
-        <v>15600</v>
+        <v>15800</v>
       </c>
       <c r="J23" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="K23" s="3">
         <v>-400</v>
@@ -1366,22 +1366,22 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>16600</v>
+        <v>16800</v>
       </c>
       <c r="E24" s="3">
-        <v>12400</v>
+        <v>12600</v>
       </c>
       <c r="F24" s="3">
         <v>6800</v>
       </c>
       <c r="G24" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="H24" s="3">
         <v>2100</v>
       </c>
       <c r="I24" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="J24" s="3">
         <v>900</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>46000</v>
+        <v>46500</v>
       </c>
       <c r="E26" s="3">
-        <v>49100</v>
+        <v>49600</v>
       </c>
       <c r="F26" s="3">
-        <v>37500</v>
+        <v>37800</v>
       </c>
       <c r="G26" s="3">
-        <v>35900</v>
+        <v>36200</v>
       </c>
       <c r="H26" s="3">
-        <v>27100</v>
+        <v>27300</v>
       </c>
       <c r="I26" s="3">
-        <v>11200</v>
+        <v>11300</v>
       </c>
       <c r="J26" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="K26" s="3">
         <v>-300</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>46000</v>
+        <v>46500</v>
       </c>
       <c r="E27" s="3">
-        <v>49100</v>
+        <v>49600</v>
       </c>
       <c r="F27" s="3">
-        <v>37500</v>
+        <v>37800</v>
       </c>
       <c r="G27" s="3">
-        <v>35900</v>
+        <v>36200</v>
       </c>
       <c r="H27" s="3">
-        <v>26900</v>
+        <v>27100</v>
       </c>
       <c r="I27" s="3">
-        <v>11100</v>
+        <v>11300</v>
       </c>
       <c r="J27" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="K27" s="3">
         <v>-300</v>
@@ -1726,19 +1726,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-19000</v>
+        <v>-19200</v>
       </c>
       <c r="E32" s="3">
-        <v>-26700</v>
+        <v>-27000</v>
       </c>
       <c r="F32" s="3">
-        <v>-16800</v>
+        <v>-17000</v>
       </c>
       <c r="G32" s="3">
         <v>-8000</v>
       </c>
       <c r="H32" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>46000</v>
+        <v>46500</v>
       </c>
       <c r="E33" s="3">
-        <v>49100</v>
+        <v>49600</v>
       </c>
       <c r="F33" s="3">
-        <v>37500</v>
+        <v>37800</v>
       </c>
       <c r="G33" s="3">
-        <v>35900</v>
+        <v>36200</v>
       </c>
       <c r="H33" s="3">
-        <v>26900</v>
+        <v>27100</v>
       </c>
       <c r="I33" s="3">
-        <v>11100</v>
+        <v>11300</v>
       </c>
       <c r="J33" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="K33" s="3">
         <v>-300</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>46000</v>
+        <v>46500</v>
       </c>
       <c r="E35" s="3">
-        <v>49100</v>
+        <v>49600</v>
       </c>
       <c r="F35" s="3">
-        <v>37500</v>
+        <v>37800</v>
       </c>
       <c r="G35" s="3">
-        <v>35900</v>
+        <v>36200</v>
       </c>
       <c r="H35" s="3">
-        <v>26900</v>
+        <v>27100</v>
       </c>
       <c r="I35" s="3">
-        <v>11100</v>
+        <v>11300</v>
       </c>
       <c r="J35" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="K35" s="3">
         <v>-300</v>
@@ -1994,22 +1994,22 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>64600</v>
+        <v>65200</v>
       </c>
       <c r="E41" s="3">
-        <v>50400</v>
+        <v>50900</v>
       </c>
       <c r="F41" s="3">
-        <v>12100</v>
+        <v>12200</v>
       </c>
       <c r="G41" s="3">
-        <v>31700</v>
+        <v>32000</v>
       </c>
       <c r="H41" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="I41" s="3">
-        <v>14200</v>
+        <v>14400</v>
       </c>
       <c r="J41" s="3">
         <v>6000</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>96800</v>
+        <v>97800</v>
       </c>
       <c r="E43" s="3">
-        <v>72600</v>
+        <v>73300</v>
       </c>
       <c r="F43" s="3">
-        <v>57200</v>
+        <v>57800</v>
       </c>
       <c r="G43" s="3">
-        <v>58000</v>
+        <v>58600</v>
       </c>
       <c r="H43" s="3">
-        <v>62600</v>
+        <v>63300</v>
       </c>
       <c r="I43" s="3">
-        <v>67800</v>
+        <v>68500</v>
       </c>
       <c r="J43" s="3">
-        <v>49800</v>
+        <v>50300</v>
       </c>
       <c r="K43" s="3">
         <v>40700</v>
@@ -2129,22 +2129,22 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>47300</v>
+        <v>47800</v>
       </c>
       <c r="E44" s="3">
-        <v>36400</v>
+        <v>36700</v>
       </c>
       <c r="F44" s="3">
-        <v>32500</v>
+        <v>32800</v>
       </c>
       <c r="G44" s="3">
-        <v>14000</v>
+        <v>14100</v>
       </c>
       <c r="H44" s="3">
-        <v>15800</v>
+        <v>15900</v>
       </c>
       <c r="I44" s="3">
-        <v>9800</v>
+        <v>9900</v>
       </c>
       <c r="J44" s="3">
         <v>3500</v>
@@ -2177,13 +2177,13 @@
         <v>6400</v>
       </c>
       <c r="E45" s="3">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="F45" s="3">
         <v>5500</v>
       </c>
       <c r="G45" s="3">
-        <v>9800</v>
+        <v>9900</v>
       </c>
       <c r="H45" s="3">
         <v>3400</v>
@@ -2192,7 +2192,7 @@
         <v>3200</v>
       </c>
       <c r="J45" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="K45" s="3">
         <v>1300</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>215100</v>
+        <v>217300</v>
       </c>
       <c r="E46" s="3">
-        <v>167900</v>
+        <v>169600</v>
       </c>
       <c r="F46" s="3">
-        <v>107300</v>
+        <v>108300</v>
       </c>
       <c r="G46" s="3">
-        <v>86900</v>
+        <v>87800</v>
       </c>
       <c r="H46" s="3">
-        <v>85800</v>
+        <v>86700</v>
       </c>
       <c r="I46" s="3">
-        <v>94500</v>
+        <v>95500</v>
       </c>
       <c r="J46" s="3">
-        <v>64800</v>
+        <v>65400</v>
       </c>
       <c r="K46" s="3">
         <v>54500</v>
@@ -2264,22 +2264,22 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>59600</v>
+        <v>60200</v>
       </c>
       <c r="E47" s="3">
-        <v>56900</v>
+        <v>57500</v>
       </c>
       <c r="F47" s="3">
-        <v>40800</v>
+        <v>41200</v>
       </c>
       <c r="G47" s="3">
-        <v>33700</v>
+        <v>34100</v>
       </c>
       <c r="H47" s="3">
-        <v>31300</v>
+        <v>31600</v>
       </c>
       <c r="I47" s="3">
-        <v>10700</v>
+        <v>10800</v>
       </c>
       <c r="J47" s="3">
         <v>300</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>842200</v>
+        <v>850700</v>
       </c>
       <c r="E48" s="3">
-        <v>482000</v>
+        <v>486900</v>
       </c>
       <c r="F48" s="3">
-        <v>477900</v>
+        <v>482700</v>
       </c>
       <c r="G48" s="3">
-        <v>474000</v>
+        <v>478800</v>
       </c>
       <c r="H48" s="3">
-        <v>444200</v>
+        <v>448700</v>
       </c>
       <c r="I48" s="3">
-        <v>769800</v>
+        <v>777600</v>
       </c>
       <c r="J48" s="3">
-        <v>203100</v>
+        <v>205100</v>
       </c>
       <c r="K48" s="3">
         <v>179300</v>
@@ -2357,7 +2357,7 @@
         <v>5500</v>
       </c>
       <c r="E49" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="F49" s="3">
         <v>3200</v>
@@ -2498,16 +2498,16 @@
         <v>4400</v>
       </c>
       <c r="G52" s="3">
-        <v>16600</v>
+        <v>16700</v>
       </c>
       <c r="H52" s="3">
-        <v>16300</v>
+        <v>16500</v>
       </c>
       <c r="I52" s="3">
-        <v>17900</v>
+        <v>18000</v>
       </c>
       <c r="J52" s="3">
-        <v>10800</v>
+        <v>10900</v>
       </c>
       <c r="K52" s="3">
         <v>19400</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1127000</v>
+        <v>1138400</v>
       </c>
       <c r="E54" s="3">
-        <v>713800</v>
+        <v>721000</v>
       </c>
       <c r="F54" s="3">
-        <v>633500</v>
+        <v>639900</v>
       </c>
       <c r="G54" s="3">
-        <v>611500</v>
+        <v>617600</v>
       </c>
       <c r="H54" s="3">
-        <v>577700</v>
+        <v>583500</v>
       </c>
       <c r="I54" s="3">
-        <v>502700</v>
+        <v>507800</v>
       </c>
       <c r="J54" s="3">
-        <v>279600</v>
+        <v>282400</v>
       </c>
       <c r="K54" s="3">
         <v>254500</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>106500</v>
+        <v>107600</v>
       </c>
       <c r="E57" s="3">
-        <v>74700</v>
+        <v>75500</v>
       </c>
       <c r="F57" s="3">
-        <v>55600</v>
+        <v>56100</v>
       </c>
       <c r="G57" s="3">
-        <v>30200</v>
+        <v>30500</v>
       </c>
       <c r="H57" s="3">
-        <v>64300</v>
+        <v>64900</v>
       </c>
       <c r="I57" s="3">
-        <v>46200</v>
+        <v>46700</v>
       </c>
       <c r="J57" s="3">
-        <v>25600</v>
+        <v>25900</v>
       </c>
       <c r="K57" s="3">
         <v>21500</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>59300</v>
+        <v>59900</v>
       </c>
       <c r="E58" s="3">
-        <v>30700</v>
+        <v>31000</v>
       </c>
       <c r="F58" s="3">
-        <v>32600</v>
+        <v>32900</v>
       </c>
       <c r="G58" s="3">
-        <v>31500</v>
+        <v>31800</v>
       </c>
       <c r="H58" s="3">
-        <v>34800</v>
+        <v>35100</v>
       </c>
       <c r="I58" s="3">
-        <v>45400</v>
+        <v>45800</v>
       </c>
       <c r="J58" s="3">
-        <v>21200</v>
+        <v>21400</v>
       </c>
       <c r="K58" s="3">
         <v>23400</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>70300</v>
+        <v>71100</v>
       </c>
       <c r="E59" s="3">
-        <v>34700</v>
+        <v>35100</v>
       </c>
       <c r="F59" s="3">
-        <v>29200</v>
+        <v>29500</v>
       </c>
       <c r="G59" s="3">
-        <v>20500</v>
+        <v>20700</v>
       </c>
       <c r="H59" s="3">
-        <v>28400</v>
+        <v>28700</v>
       </c>
       <c r="I59" s="3">
-        <v>30900</v>
+        <v>31200</v>
       </c>
       <c r="J59" s="3">
-        <v>10700</v>
+        <v>10800</v>
       </c>
       <c r="K59" s="3">
         <v>8900</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>236100</v>
+        <v>238500</v>
       </c>
       <c r="E60" s="3">
-        <v>140100</v>
+        <v>141600</v>
       </c>
       <c r="F60" s="3">
-        <v>117400</v>
+        <v>118500</v>
       </c>
       <c r="G60" s="3">
-        <v>79800</v>
+        <v>80600</v>
       </c>
       <c r="H60" s="3">
-        <v>114600</v>
+        <v>115800</v>
       </c>
       <c r="I60" s="3">
-        <v>108500</v>
+        <v>109600</v>
       </c>
       <c r="J60" s="3">
-        <v>56500</v>
+        <v>57100</v>
       </c>
       <c r="K60" s="3">
         <v>53800</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>445500</v>
+        <v>450000</v>
       </c>
       <c r="E61" s="3">
-        <v>275800</v>
+        <v>278600</v>
       </c>
       <c r="F61" s="3">
-        <v>244700</v>
+        <v>247100</v>
       </c>
       <c r="G61" s="3">
-        <v>279800</v>
+        <v>282600</v>
       </c>
       <c r="H61" s="3">
-        <v>262700</v>
+        <v>265400</v>
       </c>
       <c r="I61" s="3">
-        <v>233400</v>
+        <v>235800</v>
       </c>
       <c r="J61" s="3">
-        <v>78600</v>
+        <v>79400</v>
       </c>
       <c r="K61" s="3">
         <v>49900</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>185500</v>
+        <v>187300</v>
       </c>
       <c r="E62" s="3">
-        <v>74900</v>
+        <v>75700</v>
       </c>
       <c r="F62" s="3">
-        <v>68500</v>
+        <v>69200</v>
       </c>
       <c r="G62" s="3">
-        <v>70800</v>
+        <v>71500</v>
       </c>
       <c r="H62" s="3">
-        <v>69000</v>
+        <v>69700</v>
       </c>
       <c r="I62" s="3">
-        <v>51300</v>
+        <v>51800</v>
       </c>
       <c r="J62" s="3">
-        <v>38100</v>
+        <v>38500</v>
       </c>
       <c r="K62" s="3">
         <v>35300</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>867100</v>
+        <v>875800</v>
       </c>
       <c r="E66" s="3">
-        <v>490900</v>
+        <v>495800</v>
       </c>
       <c r="F66" s="3">
-        <v>430600</v>
+        <v>434900</v>
       </c>
       <c r="G66" s="3">
-        <v>430400</v>
+        <v>434800</v>
       </c>
       <c r="H66" s="3">
-        <v>446400</v>
+        <v>450900</v>
       </c>
       <c r="I66" s="3">
-        <v>393600</v>
+        <v>397600</v>
       </c>
       <c r="J66" s="3">
-        <v>173200</v>
+        <v>175000</v>
       </c>
       <c r="K66" s="3">
         <v>139000</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>89700</v>
+        <v>90600</v>
       </c>
       <c r="E72" s="3">
-        <v>51400</v>
+        <v>51900</v>
       </c>
       <c r="F72" s="3">
-        <v>8600</v>
+        <v>8700</v>
       </c>
       <c r="G72" s="3">
-        <v>-25600</v>
+        <v>-25900</v>
       </c>
       <c r="H72" s="3">
-        <v>-58200</v>
+        <v>-58800</v>
       </c>
       <c r="I72" s="3">
-        <v>-83000</v>
+        <v>-83900</v>
       </c>
       <c r="J72" s="3">
-        <v>-92700</v>
+        <v>-93600</v>
       </c>
       <c r="K72" s="3">
         <v>-94700</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>259900</v>
+        <v>262500</v>
       </c>
       <c r="E76" s="3">
-        <v>222900</v>
+        <v>225200</v>
       </c>
       <c r="F76" s="3">
-        <v>202900</v>
+        <v>205000</v>
       </c>
       <c r="G76" s="3">
-        <v>181100</v>
+        <v>182900</v>
       </c>
       <c r="H76" s="3">
-        <v>131300</v>
+        <v>132600</v>
       </c>
       <c r="I76" s="3">
-        <v>109100</v>
+        <v>110200</v>
       </c>
       <c r="J76" s="3">
-        <v>106300</v>
+        <v>107400</v>
       </c>
       <c r="K76" s="3">
         <v>115600</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>46000</v>
+        <v>46500</v>
       </c>
       <c r="E81" s="3">
-        <v>49100</v>
+        <v>49600</v>
       </c>
       <c r="F81" s="3">
-        <v>37500</v>
+        <v>37800</v>
       </c>
       <c r="G81" s="3">
-        <v>35900</v>
+        <v>36200</v>
       </c>
       <c r="H81" s="3">
-        <v>26900</v>
+        <v>27100</v>
       </c>
       <c r="I81" s="3">
-        <v>11100</v>
+        <v>11300</v>
       </c>
       <c r="J81" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="K81" s="3">
         <v>-300</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>95700</v>
+        <v>96700</v>
       </c>
       <c r="E83" s="3">
-        <v>86900</v>
+        <v>87800</v>
       </c>
       <c r="F83" s="3">
-        <v>78700</v>
+        <v>79500</v>
       </c>
       <c r="G83" s="3">
-        <v>65100</v>
+        <v>65800</v>
       </c>
       <c r="H83" s="3">
-        <v>74500</v>
+        <v>75300</v>
       </c>
       <c r="I83" s="3">
-        <v>42800</v>
+        <v>43300</v>
       </c>
       <c r="J83" s="3">
-        <v>33300</v>
+        <v>33600</v>
       </c>
       <c r="K83" s="3">
         <v>30900</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>197100</v>
+        <v>199000</v>
       </c>
       <c r="E89" s="3">
-        <v>123300</v>
+        <v>124600</v>
       </c>
       <c r="F89" s="3">
-        <v>120400</v>
+        <v>121600</v>
       </c>
       <c r="G89" s="3">
-        <v>106800</v>
+        <v>107900</v>
       </c>
       <c r="H89" s="3">
-        <v>115100</v>
+        <v>116300</v>
       </c>
       <c r="I89" s="3">
-        <v>79700</v>
+        <v>80500</v>
       </c>
       <c r="J89" s="3">
-        <v>36300</v>
+        <v>36600</v>
       </c>
       <c r="K89" s="3">
         <v>29000</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-147800</v>
+        <v>-149300</v>
       </c>
       <c r="E91" s="3">
-        <v>-81300</v>
+        <v>-82100</v>
       </c>
       <c r="F91" s="3">
-        <v>-82000</v>
+        <v>-82900</v>
       </c>
       <c r="G91" s="3">
-        <v>-85300</v>
+        <v>-86200</v>
       </c>
       <c r="H91" s="3">
-        <v>-114400</v>
+        <v>-115600</v>
       </c>
       <c r="I91" s="3">
-        <v>-59100</v>
+        <v>-59700</v>
       </c>
       <c r="J91" s="3">
-        <v>-39200</v>
+        <v>-39600</v>
       </c>
       <c r="K91" s="3">
         <v>-19700</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-178500</v>
+        <v>-180300</v>
       </c>
       <c r="E94" s="3">
-        <v>-71000</v>
+        <v>-71700</v>
       </c>
       <c r="F94" s="3">
-        <v>-72300</v>
+        <v>-73100</v>
       </c>
       <c r="G94" s="3">
-        <v>-82200</v>
+        <v>-83100</v>
       </c>
       <c r="H94" s="3">
-        <v>-117100</v>
+        <v>-118300</v>
       </c>
       <c r="I94" s="3">
-        <v>-166600</v>
+        <v>-168300</v>
       </c>
       <c r="J94" s="3">
-        <v>-24500</v>
+        <v>-24700</v>
       </c>
       <c r="K94" s="3">
         <v>-7600</v>
@@ -4228,19 +4228,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-7300</v>
+        <v>-7400</v>
       </c>
       <c r="E96" s="3">
         <v>-5700</v>
       </c>
       <c r="F96" s="3">
-        <v>-3200</v>
+        <v>-3300</v>
       </c>
       <c r="G96" s="3">
         <v>-3200</v>
       </c>
       <c r="H96" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="I96" s="3">
         <v>-1500</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-5600</v>
+        <v>-5700</v>
       </c>
       <c r="E100" s="3">
-        <v>-14200</v>
+        <v>-14300</v>
       </c>
       <c r="F100" s="3">
-        <v>-67600</v>
+        <v>-68300</v>
       </c>
       <c r="G100" s="3">
         <v>3300</v>
       </c>
       <c r="H100" s="3">
-        <v>-8200</v>
+        <v>-8300</v>
       </c>
       <c r="I100" s="3">
-        <v>95200</v>
+        <v>96100</v>
       </c>
       <c r="J100" s="3">
-        <v>-15800</v>
+        <v>-15900</v>
       </c>
       <c r="K100" s="3">
         <v>-34900</v>
@@ -4453,7 +4453,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E101" s="3">
         <v>200</v>
@@ -4498,19 +4498,19 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>14200</v>
+        <v>14300</v>
       </c>
       <c r="E102" s="3">
-        <v>38300</v>
+        <v>38700</v>
       </c>
       <c r="F102" s="3">
-        <v>-19600</v>
+        <v>-19800</v>
       </c>
       <c r="G102" s="3">
-        <v>27900</v>
+        <v>28100</v>
       </c>
       <c r="H102" s="3">
-        <v>-10200</v>
+        <v>-10300</v>
       </c>
       <c r="I102" s="3">
         <v>8300</v>

--- a/AAII_Financials/Yearly/NOA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NOA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>NOA</t>
   </si>
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>704600</v>
+        <v>724800</v>
       </c>
       <c r="E8" s="3">
-        <v>566500</v>
+        <v>568600</v>
       </c>
       <c r="F8" s="3">
-        <v>481500</v>
+        <v>516900</v>
       </c>
       <c r="G8" s="3">
-        <v>366900</v>
+        <v>391200</v>
       </c>
       <c r="H8" s="3">
-        <v>529300</v>
+        <v>554400</v>
       </c>
       <c r="I8" s="3">
-        <v>301900</v>
+        <v>300500</v>
       </c>
       <c r="J8" s="3">
-        <v>215400</v>
+        <v>233300</v>
       </c>
       <c r="K8" s="3">
         <v>155000</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>591100</v>
+        <v>508600</v>
       </c>
       <c r="E9" s="3">
-        <v>491700</v>
+        <v>405400</v>
       </c>
       <c r="F9" s="3">
-        <v>424200</v>
+        <v>370000</v>
       </c>
       <c r="G9" s="3">
-        <v>317600</v>
+        <v>268900</v>
       </c>
       <c r="H9" s="3">
-        <v>458300</v>
+        <v>401700</v>
       </c>
       <c r="I9" s="3">
-        <v>251000</v>
+        <v>207100</v>
       </c>
       <c r="J9" s="3">
-        <v>186200</v>
+        <v>166000</v>
       </c>
       <c r="K9" s="3">
         <v>131500</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>113500</v>
+        <v>216200</v>
       </c>
       <c r="E10" s="3">
-        <v>74800</v>
+        <v>163200</v>
       </c>
       <c r="F10" s="3">
-        <v>57400</v>
+        <v>146900</v>
       </c>
       <c r="G10" s="3">
-        <v>49400</v>
+        <v>122300</v>
       </c>
       <c r="H10" s="3">
-        <v>71000</v>
+        <v>152700</v>
       </c>
       <c r="I10" s="3">
-        <v>50800</v>
+        <v>93400</v>
       </c>
       <c r="J10" s="3">
-        <v>29200</v>
+        <v>67300</v>
       </c>
       <c r="K10" s="3">
         <v>23500</v>
@@ -970,26 +970,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>500</v>
       </c>
       <c r="F14" s="3">
-        <v>-9600</v>
+        <v>-10500</v>
       </c>
       <c r="G14" s="3">
-        <v>-20600</v>
+        <v>-21500</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J14" s="3">
         <v>1300</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1015,26 +1015,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>99400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>88100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>85400</v>
       </c>
       <c r="G15" s="3">
-        <v>400</v>
+        <v>69700</v>
       </c>
       <c r="H15" s="3">
-        <v>500</v>
+        <v>78900</v>
       </c>
       <c r="I15" s="3">
-        <v>300</v>
+        <v>43100</v>
       </c>
       <c r="J15" s="3">
-        <v>700</v>
+        <v>35100</v>
       </c>
       <c r="K15" s="3">
         <v>1200</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>634200</v>
+        <v>651100</v>
       </c>
       <c r="E17" s="3">
-        <v>514100</v>
+        <v>515500</v>
       </c>
       <c r="F17" s="3">
-        <v>440900</v>
+        <v>483900</v>
       </c>
       <c r="G17" s="3">
-        <v>317500</v>
+        <v>360000</v>
       </c>
       <c r="H17" s="3">
-        <v>486000</v>
+        <v>509100</v>
       </c>
       <c r="I17" s="3">
-        <v>279800</v>
+        <v>278700</v>
       </c>
       <c r="J17" s="3">
-        <v>205500</v>
+        <v>221300</v>
       </c>
       <c r="K17" s="3">
         <v>152100</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>70500</v>
+        <v>73700</v>
       </c>
       <c r="E18" s="3">
-        <v>52400</v>
+        <v>53000</v>
       </c>
       <c r="F18" s="3">
-        <v>40600</v>
+        <v>33000</v>
       </c>
       <c r="G18" s="3">
-        <v>49400</v>
+        <v>31200</v>
       </c>
       <c r="H18" s="3">
-        <v>43300</v>
+        <v>45300</v>
       </c>
       <c r="I18" s="3">
-        <v>22100</v>
+        <v>21900</v>
       </c>
       <c r="J18" s="3">
-        <v>9900</v>
+        <v>12000</v>
       </c>
       <c r="K18" s="3">
         <v>2900</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>19200</v>
+        <v>-24100</v>
       </c>
       <c r="E20" s="3">
-        <v>27000</v>
+        <v>-28000</v>
       </c>
       <c r="F20" s="3">
-        <v>17000</v>
+        <v>-19400</v>
       </c>
       <c r="G20" s="3">
-        <v>8000</v>
+        <v>-9400</v>
       </c>
       <c r="H20" s="3">
-        <v>2000</v>
+        <v>-2100</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>1100</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>186300</v>
+        <v>197300</v>
       </c>
       <c r="E21" s="3">
-        <v>167200</v>
+        <v>169100</v>
       </c>
       <c r="F21" s="3">
-        <v>137100</v>
+        <v>137800</v>
       </c>
       <c r="G21" s="3">
-        <v>123300</v>
+        <v>110300</v>
       </c>
       <c r="H21" s="3">
-        <v>120600</v>
+        <v>126300</v>
       </c>
       <c r="I21" s="3">
-        <v>65500</v>
+        <v>64900</v>
       </c>
       <c r="J21" s="3">
-        <v>43600</v>
+        <v>47100</v>
       </c>
       <c r="K21" s="3">
         <v>35000</v>
@@ -1276,25 +1276,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>26300</v>
+        <v>28000</v>
       </c>
       <c r="E22" s="3">
-        <v>17200</v>
+        <v>18100</v>
       </c>
       <c r="F22" s="3">
-        <v>12900</v>
+        <v>15100</v>
       </c>
       <c r="G22" s="3">
-        <v>12900</v>
+        <v>14800</v>
       </c>
       <c r="H22" s="3">
-        <v>15800</v>
+        <v>16800</v>
       </c>
       <c r="I22" s="3">
         <v>6400</v>
       </c>
       <c r="J22" s="3">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="K22" s="3">
         <v>4300</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>63300</v>
+        <v>65100</v>
       </c>
       <c r="E23" s="3">
-        <v>62200</v>
+        <v>62400</v>
       </c>
       <c r="F23" s="3">
-        <v>44700</v>
+        <v>48000</v>
       </c>
       <c r="G23" s="3">
-        <v>44500</v>
+        <v>47500</v>
       </c>
       <c r="H23" s="3">
-        <v>29400</v>
+        <v>30800</v>
       </c>
       <c r="I23" s="3">
-        <v>15800</v>
+        <v>15700</v>
       </c>
       <c r="J23" s="3">
-        <v>4800</v>
+        <v>5200</v>
       </c>
       <c r="K23" s="3">
         <v>-400</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>16800</v>
+        <v>17300</v>
       </c>
       <c r="E24" s="3">
         <v>12600</v>
       </c>
       <c r="F24" s="3">
-        <v>6800</v>
+        <v>7300</v>
       </c>
       <c r="G24" s="3">
-        <v>8300</v>
+        <v>8800</v>
       </c>
       <c r="H24" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="I24" s="3">
         <v>4500</v>
       </c>
       <c r="J24" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>46500</v>
+        <v>47800</v>
       </c>
       <c r="E26" s="3">
-        <v>49600</v>
+        <v>49800</v>
       </c>
       <c r="F26" s="3">
-        <v>37800</v>
+        <v>40600</v>
       </c>
       <c r="G26" s="3">
-        <v>36200</v>
+        <v>38600</v>
       </c>
       <c r="H26" s="3">
-        <v>27300</v>
+        <v>28600</v>
       </c>
       <c r="I26" s="3">
-        <v>11300</v>
+        <v>11200</v>
       </c>
       <c r="J26" s="3">
-        <v>3900</v>
+        <v>4200</v>
       </c>
       <c r="K26" s="3">
         <v>-300</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>46500</v>
+        <v>47800</v>
       </c>
       <c r="E27" s="3">
-        <v>49600</v>
+        <v>49800</v>
       </c>
       <c r="F27" s="3">
-        <v>37800</v>
+        <v>40600</v>
       </c>
       <c r="G27" s="3">
-        <v>36200</v>
+        <v>38600</v>
       </c>
       <c r="H27" s="3">
-        <v>27100</v>
+        <v>28400</v>
       </c>
       <c r="I27" s="3">
-        <v>11300</v>
+        <v>11200</v>
       </c>
       <c r="J27" s="3">
-        <v>3900</v>
+        <v>4200</v>
       </c>
       <c r="K27" s="3">
         <v>-300</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-19200</v>
+        <v>24100</v>
       </c>
       <c r="E32" s="3">
-        <v>-27000</v>
+        <v>28000</v>
       </c>
       <c r="F32" s="3">
-        <v>-17000</v>
+        <v>19400</v>
       </c>
       <c r="G32" s="3">
-        <v>-8000</v>
+        <v>9400</v>
       </c>
       <c r="H32" s="3">
-        <v>-2000</v>
+        <v>2100</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-1100</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>46500</v>
+        <v>47800</v>
       </c>
       <c r="E33" s="3">
-        <v>49600</v>
+        <v>49800</v>
       </c>
       <c r="F33" s="3">
-        <v>37800</v>
+        <v>40600</v>
       </c>
       <c r="G33" s="3">
-        <v>36200</v>
+        <v>38600</v>
       </c>
       <c r="H33" s="3">
-        <v>27100</v>
+        <v>28400</v>
       </c>
       <c r="I33" s="3">
-        <v>11300</v>
+        <v>11200</v>
       </c>
       <c r="J33" s="3">
-        <v>3900</v>
+        <v>4200</v>
       </c>
       <c r="K33" s="3">
         <v>-300</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>46500</v>
+        <v>47800</v>
       </c>
       <c r="E35" s="3">
-        <v>49600</v>
+        <v>49800</v>
       </c>
       <c r="F35" s="3">
-        <v>37800</v>
+        <v>40600</v>
       </c>
       <c r="G35" s="3">
-        <v>36200</v>
+        <v>38600</v>
       </c>
       <c r="H35" s="3">
-        <v>27100</v>
+        <v>28400</v>
       </c>
       <c r="I35" s="3">
-        <v>11300</v>
+        <v>11200</v>
       </c>
       <c r="J35" s="3">
-        <v>3900</v>
+        <v>4200</v>
       </c>
       <c r="K35" s="3">
         <v>-300</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>65200</v>
+        <v>67100</v>
       </c>
       <c r="E41" s="3">
-        <v>50900</v>
+        <v>51100</v>
       </c>
       <c r="F41" s="3">
-        <v>12200</v>
+        <v>13100</v>
       </c>
       <c r="G41" s="3">
-        <v>32000</v>
+        <v>34100</v>
       </c>
       <c r="H41" s="3">
-        <v>4100</v>
+        <v>4300</v>
       </c>
       <c r="I41" s="3">
-        <v>14400</v>
+        <v>14300</v>
       </c>
       <c r="J41" s="3">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="K41" s="3">
         <v>9900</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>97800</v>
+        <v>100600</v>
       </c>
       <c r="E43" s="3">
-        <v>73300</v>
+        <v>73600</v>
       </c>
       <c r="F43" s="3">
-        <v>57800</v>
+        <v>62100</v>
       </c>
       <c r="G43" s="3">
-        <v>58600</v>
+        <v>33900</v>
       </c>
       <c r="H43" s="3">
-        <v>63300</v>
+        <v>66300</v>
       </c>
       <c r="I43" s="3">
-        <v>68500</v>
+        <v>68200</v>
       </c>
       <c r="J43" s="3">
-        <v>50300</v>
+        <v>54500</v>
       </c>
       <c r="K43" s="3">
         <v>40700</v>
@@ -2129,25 +2129,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>47800</v>
+        <v>49200</v>
       </c>
       <c r="E44" s="3">
-        <v>36700</v>
+        <v>36900</v>
       </c>
       <c r="F44" s="3">
-        <v>32800</v>
+        <v>35200</v>
       </c>
       <c r="G44" s="3">
-        <v>14100</v>
+        <v>15000</v>
       </c>
       <c r="H44" s="3">
-        <v>15900</v>
+        <v>16700</v>
       </c>
       <c r="I44" s="3">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="J44" s="3">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="K44" s="3">
         <v>2500</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6400</v>
+        <v>1000</v>
       </c>
       <c r="E45" s="3">
-        <v>8600</v>
+        <v>800</v>
       </c>
       <c r="F45" s="3">
-        <v>5500</v>
+        <v>500</v>
       </c>
       <c r="G45" s="3">
-        <v>9900</v>
+        <v>6600</v>
       </c>
       <c r="H45" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3200</v>
+        <v>300</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J45" s="3">
-        <v>5600</v>
+        <v>5300</v>
       </c>
       <c r="K45" s="3">
         <v>1300</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>217300</v>
+        <v>223500</v>
       </c>
       <c r="E46" s="3">
-        <v>169600</v>
+        <v>170200</v>
       </c>
       <c r="F46" s="3">
-        <v>108300</v>
+        <v>116300</v>
       </c>
       <c r="G46" s="3">
-        <v>87800</v>
+        <v>93600</v>
       </c>
       <c r="H46" s="3">
-        <v>86700</v>
+        <v>90800</v>
       </c>
       <c r="I46" s="3">
-        <v>95500</v>
+        <v>95100</v>
       </c>
       <c r="J46" s="3">
-        <v>65400</v>
+        <v>70900</v>
       </c>
       <c r="K46" s="3">
         <v>54500</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>60200</v>
+        <v>61700</v>
       </c>
       <c r="E47" s="3">
-        <v>57500</v>
+        <v>55900</v>
       </c>
       <c r="F47" s="3">
-        <v>41200</v>
+        <v>44200</v>
       </c>
       <c r="G47" s="3">
-        <v>34100</v>
+        <v>36300</v>
       </c>
       <c r="H47" s="3">
-        <v>31600</v>
+        <v>33100</v>
       </c>
       <c r="I47" s="3">
-        <v>10800</v>
-      </c>
-      <c r="J47" s="3">
-        <v>300</v>
+        <v>8600</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>850700</v>
+        <v>875100</v>
       </c>
       <c r="E48" s="3">
-        <v>486900</v>
+        <v>488100</v>
       </c>
       <c r="F48" s="3">
-        <v>482700</v>
+        <v>518200</v>
       </c>
       <c r="G48" s="3">
-        <v>478800</v>
+        <v>510400</v>
       </c>
       <c r="H48" s="3">
-        <v>448700</v>
+        <v>470000</v>
       </c>
       <c r="I48" s="3">
-        <v>777600</v>
+        <v>387100</v>
       </c>
       <c r="J48" s="3">
-        <v>205100</v>
+        <v>222200</v>
       </c>
       <c r="K48" s="3">
         <v>179300</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="E49" s="3">
         <v>5400</v>
       </c>
       <c r="F49" s="3">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="G49" s="3">
         <v>300</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>8</v>
+      <c r="H49" s="3">
+        <v>0</v>
       </c>
       <c r="I49" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="K49" s="3">
         <v>1300</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4600</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>1700</v>
+        <v>1400</v>
       </c>
       <c r="F52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G52" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H52" s="3">
         <v>4400</v>
       </c>
-      <c r="G52" s="3">
-        <v>16700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>16500</v>
-      </c>
       <c r="I52" s="3">
-        <v>18000</v>
+        <v>6300</v>
       </c>
       <c r="J52" s="3">
-        <v>10900</v>
+        <v>1400</v>
       </c>
       <c r="K52" s="3">
         <v>19400</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1138400</v>
+        <v>1171000</v>
       </c>
       <c r="E54" s="3">
-        <v>721000</v>
+        <v>723700</v>
       </c>
       <c r="F54" s="3">
-        <v>639900</v>
+        <v>686900</v>
       </c>
       <c r="G54" s="3">
-        <v>617600</v>
+        <v>658500</v>
       </c>
       <c r="H54" s="3">
-        <v>583500</v>
+        <v>611100</v>
       </c>
       <c r="I54" s="3">
-        <v>507800</v>
+        <v>505500</v>
       </c>
       <c r="J54" s="3">
-        <v>282400</v>
+        <v>305900</v>
       </c>
       <c r="K54" s="3">
         <v>254500</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>107600</v>
+        <v>110700</v>
       </c>
       <c r="E57" s="3">
-        <v>75500</v>
+        <v>75800</v>
       </c>
       <c r="F57" s="3">
-        <v>56100</v>
+        <v>60300</v>
       </c>
       <c r="G57" s="3">
-        <v>30500</v>
+        <v>32500</v>
       </c>
       <c r="H57" s="3">
-        <v>64900</v>
+        <v>68000</v>
       </c>
       <c r="I57" s="3">
-        <v>46700</v>
+        <v>46500</v>
       </c>
       <c r="J57" s="3">
-        <v>25900</v>
+        <v>28100</v>
       </c>
       <c r="K57" s="3">
         <v>21500</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>59900</v>
+        <v>71500</v>
       </c>
       <c r="E58" s="3">
-        <v>31000</v>
+        <v>32900</v>
       </c>
       <c r="F58" s="3">
-        <v>32900</v>
+        <v>38000</v>
       </c>
       <c r="G58" s="3">
-        <v>31800</v>
+        <v>37000</v>
       </c>
       <c r="H58" s="3">
-        <v>35100</v>
+        <v>39700</v>
       </c>
       <c r="I58" s="3">
-        <v>45800</v>
+        <v>45600</v>
       </c>
       <c r="J58" s="3">
-        <v>21400</v>
+        <v>23400</v>
       </c>
       <c r="K58" s="3">
         <v>23400</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>71100</v>
+        <v>39200</v>
       </c>
       <c r="E59" s="3">
-        <v>35100</v>
+        <v>17400</v>
       </c>
       <c r="F59" s="3">
-        <v>29500</v>
+        <v>11200</v>
       </c>
       <c r="G59" s="3">
-        <v>20700</v>
+        <v>4600</v>
       </c>
       <c r="H59" s="3">
-        <v>28700</v>
+        <v>800</v>
       </c>
       <c r="I59" s="3">
-        <v>31200</v>
+        <v>4600</v>
       </c>
       <c r="J59" s="3">
-        <v>10800</v>
+        <v>2800</v>
       </c>
       <c r="K59" s="3">
         <v>8900</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>238500</v>
+        <v>245400</v>
       </c>
       <c r="E60" s="3">
-        <v>141600</v>
+        <v>142100</v>
       </c>
       <c r="F60" s="3">
-        <v>118500</v>
+        <v>127300</v>
       </c>
       <c r="G60" s="3">
-        <v>80600</v>
+        <v>85900</v>
       </c>
       <c r="H60" s="3">
-        <v>115800</v>
+        <v>121300</v>
       </c>
       <c r="I60" s="3">
-        <v>109600</v>
+        <v>109100</v>
       </c>
       <c r="J60" s="3">
-        <v>57100</v>
+        <v>61900</v>
       </c>
       <c r="K60" s="3">
         <v>53800</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>450000</v>
+        <v>471500</v>
       </c>
       <c r="E61" s="3">
-        <v>278600</v>
+        <v>288800</v>
       </c>
       <c r="F61" s="3">
-        <v>247100</v>
+        <v>274300</v>
       </c>
       <c r="G61" s="3">
-        <v>282600</v>
+        <v>312400</v>
       </c>
       <c r="H61" s="3">
-        <v>265400</v>
+        <v>291600</v>
       </c>
       <c r="I61" s="3">
-        <v>235800</v>
+        <v>234700</v>
       </c>
       <c r="J61" s="3">
-        <v>79400</v>
+        <v>86000</v>
       </c>
       <c r="K61" s="3">
         <v>49900</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>187300</v>
+        <v>89500</v>
       </c>
       <c r="E62" s="3">
-        <v>75700</v>
+        <v>13700</v>
       </c>
       <c r="F62" s="3">
-        <v>69200</v>
+        <v>18500</v>
       </c>
       <c r="G62" s="3">
-        <v>71500</v>
+        <v>11100</v>
       </c>
       <c r="H62" s="3">
-        <v>69700</v>
+        <v>13800</v>
       </c>
       <c r="I62" s="3">
-        <v>51800</v>
+        <v>12600</v>
       </c>
       <c r="J62" s="3">
-        <v>38500</v>
+        <v>5100</v>
       </c>
       <c r="K62" s="3">
         <v>35300</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>875800</v>
+        <v>901000</v>
       </c>
       <c r="E66" s="3">
-        <v>495800</v>
+        <v>497700</v>
       </c>
       <c r="F66" s="3">
-        <v>434900</v>
+        <v>466900</v>
       </c>
       <c r="G66" s="3">
-        <v>434800</v>
+        <v>463500</v>
       </c>
       <c r="H66" s="3">
-        <v>450900</v>
+        <v>472300</v>
       </c>
       <c r="I66" s="3">
-        <v>397600</v>
+        <v>395400</v>
       </c>
       <c r="J66" s="3">
-        <v>175000</v>
+        <v>189600</v>
       </c>
       <c r="K66" s="3">
         <v>139000</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>90600</v>
+        <v>93200</v>
       </c>
       <c r="E72" s="3">
-        <v>51900</v>
+        <v>52100</v>
       </c>
       <c r="F72" s="3">
-        <v>8700</v>
+        <v>9400</v>
       </c>
       <c r="G72" s="3">
-        <v>-25900</v>
+        <v>-27600</v>
       </c>
       <c r="H72" s="3">
-        <v>-58800</v>
+        <v>-61600</v>
       </c>
       <c r="I72" s="3">
-        <v>-83900</v>
+        <v>-83500</v>
       </c>
       <c r="J72" s="3">
-        <v>-93600</v>
+        <v>-101400</v>
       </c>
       <c r="K72" s="3">
         <v>-94700</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>262500</v>
+        <v>270100</v>
       </c>
       <c r="E76" s="3">
-        <v>225200</v>
+        <v>226000</v>
       </c>
       <c r="F76" s="3">
-        <v>205000</v>
+        <v>220000</v>
       </c>
       <c r="G76" s="3">
-        <v>182900</v>
+        <v>195000</v>
       </c>
       <c r="H76" s="3">
-        <v>132600</v>
+        <v>138900</v>
       </c>
       <c r="I76" s="3">
-        <v>110200</v>
+        <v>109700</v>
       </c>
       <c r="J76" s="3">
-        <v>107400</v>
+        <v>116400</v>
       </c>
       <c r="K76" s="3">
         <v>115600</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>46500</v>
+        <v>47800</v>
       </c>
       <c r="E81" s="3">
-        <v>49600</v>
+        <v>49800</v>
       </c>
       <c r="F81" s="3">
-        <v>37800</v>
+        <v>40600</v>
       </c>
       <c r="G81" s="3">
-        <v>36200</v>
+        <v>38600</v>
       </c>
       <c r="H81" s="3">
-        <v>27100</v>
+        <v>28400</v>
       </c>
       <c r="I81" s="3">
-        <v>11300</v>
+        <v>11200</v>
       </c>
       <c r="J81" s="3">
-        <v>3900</v>
+        <v>4200</v>
       </c>
       <c r="K81" s="3">
         <v>-300</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>96700</v>
+        <v>99400</v>
       </c>
       <c r="E83" s="3">
-        <v>87800</v>
+        <v>88100</v>
       </c>
       <c r="F83" s="3">
-        <v>79500</v>
+        <v>85400</v>
       </c>
       <c r="G83" s="3">
-        <v>65800</v>
+        <v>69700</v>
       </c>
       <c r="H83" s="3">
-        <v>75300</v>
+        <v>78300</v>
       </c>
       <c r="I83" s="3">
-        <v>43300</v>
+        <v>42800</v>
       </c>
       <c r="J83" s="3">
-        <v>33600</v>
+        <v>34400</v>
       </c>
       <c r="K83" s="3">
         <v>30900</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>199000</v>
+        <v>204700</v>
       </c>
       <c r="E89" s="3">
-        <v>124600</v>
+        <v>125000</v>
       </c>
       <c r="F89" s="3">
-        <v>121600</v>
+        <v>130500</v>
       </c>
       <c r="G89" s="3">
-        <v>107900</v>
+        <v>115000</v>
       </c>
       <c r="H89" s="3">
-        <v>116300</v>
+        <v>121800</v>
       </c>
       <c r="I89" s="3">
-        <v>80500</v>
+        <v>80200</v>
       </c>
       <c r="J89" s="3">
-        <v>36600</v>
+        <v>39700</v>
       </c>
       <c r="K89" s="3">
         <v>29000</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-149300</v>
+        <v>-153600</v>
       </c>
       <c r="E91" s="3">
-        <v>-82100</v>
+        <v>-82400</v>
       </c>
       <c r="F91" s="3">
-        <v>-82900</v>
+        <v>-88900</v>
       </c>
       <c r="G91" s="3">
-        <v>-86200</v>
+        <v>-91900</v>
       </c>
       <c r="H91" s="3">
-        <v>-115600</v>
+        <v>-121100</v>
       </c>
       <c r="I91" s="3">
-        <v>-59700</v>
+        <v>-170200</v>
       </c>
       <c r="J91" s="3">
-        <v>-39600</v>
+        <v>-42900</v>
       </c>
       <c r="K91" s="3">
         <v>-19700</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-180300</v>
+        <v>-185400</v>
       </c>
       <c r="E94" s="3">
-        <v>-71700</v>
+        <v>-72000</v>
       </c>
       <c r="F94" s="3">
-        <v>-73100</v>
+        <v>-78400</v>
       </c>
       <c r="G94" s="3">
-        <v>-83100</v>
+        <v>-88500</v>
       </c>
       <c r="H94" s="3">
-        <v>-118300</v>
+        <v>-123900</v>
       </c>
       <c r="I94" s="3">
-        <v>-168300</v>
+        <v>-167500</v>
       </c>
       <c r="J94" s="3">
-        <v>-24700</v>
+        <v>-26800</v>
       </c>
       <c r="K94" s="3">
         <v>-7600</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-7400</v>
+        <v>7600</v>
       </c>
       <c r="E96" s="3">
-        <v>-5700</v>
+        <v>5700</v>
       </c>
       <c r="F96" s="3">
-        <v>-3300</v>
+        <v>3500</v>
       </c>
       <c r="G96" s="3">
-        <v>-3200</v>
+        <v>3400</v>
       </c>
       <c r="H96" s="3">
-        <v>-1900</v>
+        <v>2000</v>
       </c>
       <c r="I96" s="3">
-        <v>-1500</v>
+        <v>1500</v>
       </c>
       <c r="J96" s="3">
-        <v>-1600</v>
+        <v>1700</v>
       </c>
       <c r="K96" s="3">
         <v>-1300</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-5700</v>
+        <v>-5900</v>
       </c>
       <c r="E100" s="3">
-        <v>-14300</v>
+        <v>-14400</v>
       </c>
       <c r="F100" s="3">
-        <v>-68300</v>
+        <v>-73300</v>
       </c>
       <c r="G100" s="3">
-        <v>3300</v>
+        <v>3500</v>
       </c>
       <c r="H100" s="3">
-        <v>-8300</v>
+        <v>-8700</v>
       </c>
       <c r="I100" s="3">
-        <v>96100</v>
+        <v>95700</v>
       </c>
       <c r="J100" s="3">
-        <v>-15900</v>
+        <v>-17200</v>
       </c>
       <c r="K100" s="3">
         <v>-34900</v>
@@ -4461,8 +4461,8 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>8</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>14300</v>
+        <v>14700</v>
       </c>
       <c r="E102" s="3">
-        <v>38700</v>
+        <v>38800</v>
       </c>
       <c r="F102" s="3">
-        <v>-19800</v>
+        <v>-21200</v>
       </c>
       <c r="G102" s="3">
-        <v>28100</v>
+        <v>30000</v>
       </c>
       <c r="H102" s="3">
-        <v>-10300</v>
+        <v>-10800</v>
       </c>
       <c r="I102" s="3">
         <v>8300</v>
       </c>
       <c r="J102" s="3">
-        <v>-4000</v>
+        <v>-4400</v>
       </c>
       <c r="K102" s="3">
         <v>-13600</v>

--- a/AAII_Financials/Yearly/NOA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NOA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>NOA</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41364</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>724800</v>
+        <v>810200</v>
       </c>
       <c r="E8" s="3">
+        <v>730500</v>
+      </c>
+      <c r="F8" s="3">
         <v>568600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>516900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>391200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>554400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>300500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>233300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>155000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>211200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>370400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>362200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>410000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>515300</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>508600</v>
+        <v>548400</v>
       </c>
       <c r="E9" s="3">
+        <v>513800</v>
+      </c>
+      <c r="F9" s="3">
         <v>405400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>370000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>268900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>401700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>207100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>166000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>131500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>187300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>330000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>327000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>384500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>490700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>216200</v>
+        <v>261800</v>
       </c>
       <c r="E10" s="3">
+        <v>216700</v>
+      </c>
+      <c r="F10" s="3">
         <v>163200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>146900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>122300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>152700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>93400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>67300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>40400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>35200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>24600</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,8 +887,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,99 +980,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E14" s="3">
         <v>4800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-10500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-21500</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>5000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E15" s="3">
         <v>99400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>88100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>85400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>69700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>78900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>43100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3300</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>651100</v>
+        <v>703100</v>
       </c>
       <c r="E17" s="3">
+        <v>656300</v>
+      </c>
+      <c r="F17" s="3">
         <v>515500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>483900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>360000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>509100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>278700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>221300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>152100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>209500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>361300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>369200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>422000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>526600</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>73700</v>
+        <v>107100</v>
       </c>
       <c r="E18" s="3">
+        <v>74200</v>
+      </c>
+      <c r="F18" s="3">
         <v>53000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>33000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>31200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>45300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>21900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-12100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,233 +1212,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-24100</v>
+        <v>-13400</v>
       </c>
       <c r="E20" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-28000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-19400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-15900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>236300</v>
+      </c>
+      <c r="E21" s="3">
         <v>197300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>169100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>137800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>110300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>126300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>64900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>47100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>35000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>45400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>28900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12400</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E22" s="3">
         <v>28000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>18100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16900</v>
       </c>
-      <c r="O22" s="3" t="s">
+      <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1200</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E23" s="3">
         <v>65100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>62400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>48000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>47500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>30800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>15700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E24" s="3">
         <v>17300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-4700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-6700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E26" s="3">
         <v>47800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>49800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>40600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>38600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>28600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-19500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E27" s="3">
         <v>47800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>49800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>40600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>38600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>28400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-19500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1618,20 +1678,23 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>67200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>20200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>3200</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>24100</v>
+        <v>13400</v>
       </c>
       <c r="E32" s="3">
+        <v>23700</v>
+      </c>
+      <c r="F32" s="3">
         <v>28000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>19400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>15900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>14000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E33" s="3">
         <v>47800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>49800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>40600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>38600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>28400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>53300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E35" s="3">
         <v>47800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>49800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>40600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>38600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>28400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>53300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41364</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,53 +2073,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>54100</v>
+      </c>
+      <c r="E41" s="3">
         <v>67100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>51100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1100</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2075,214 +2164,229 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>1200</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>118300</v>
+      </c>
+      <c r="E43" s="3">
         <v>100600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>73600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>62100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>33900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>66300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>68200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>54500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>40700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>31800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>138700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>78800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>117900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>231200</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E44" s="3">
         <v>49200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>36900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>35200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>15000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>29400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>145800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9600</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>229700</v>
+      </c>
+      <c r="E46" s="3">
         <v>223500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>170200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>116300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>93600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>90800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>95100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>70900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>54500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>59400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>118000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>98400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>268500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>251200</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E47" s="3">
         <v>61700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>55900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>44200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>36300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>33100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8600</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -2299,102 +2403,111 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>875200</v>
+      </c>
+      <c r="E48" s="3">
         <v>875100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>488100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>518200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>510400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>470000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>387100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>222200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>179300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>388600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>204800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>194000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>210200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>245000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E49" s="3">
         <v>5700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>300</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3400</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>6500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>35200</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E52" s="3">
         <v>300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>32100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>50600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>46200</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1177500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1171000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>723700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>686900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>658500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>611100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>505500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>305900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>254500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>270400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>358400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>343100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>496800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>576200</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,278 +2785,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E57" s="3">
         <v>110700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>75800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>60300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>68000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>46500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>28100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>21500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>37300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>55500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>131500</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E58" s="3">
         <v>71500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>32900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>38000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>37000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>39700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>45600</v>
-      </c>
-      <c r="J58" s="3">
-        <v>23400</v>
       </c>
       <c r="K58" s="3">
         <v>23400</v>
       </c>
       <c r="L58" s="3">
+        <v>23400</v>
+      </c>
+      <c r="M58" s="3">
         <v>22500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>17400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>16100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>22100</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E59" s="3">
         <v>39200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>23100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>72300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>53000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>219500</v>
+      </c>
+      <c r="E60" s="3">
         <v>245400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>142100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>127300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>85900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>121300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>109100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>61900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>53800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>46700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>74800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>72000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>143900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>195600</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>507900</v>
+      </c>
+      <c r="E61" s="3">
         <v>471500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>288800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>274300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>312400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>291600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>234700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>86000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>49900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>60400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>83300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>79500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>218800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>230500</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>79400</v>
+      </c>
+      <c r="E62" s="3">
         <v>89500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>35300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>34400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>51500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>43900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>37700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>51900</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>907200</v>
+      </c>
+      <c r="E66" s="3">
         <v>901000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>497700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>466900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>463500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>472300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>395400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>189600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>139000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>141600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>209600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>195400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>400500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>478000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E72" s="3">
         <v>93200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>52100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-27600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-61600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-83500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-101400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-94700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-95700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-92200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-87300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-141000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-142800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>270300</v>
+      </c>
+      <c r="E76" s="3">
         <v>270100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>226000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>220000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>195000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>138900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>109700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>116400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>115600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>128900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>148800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>147700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>96300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>98200</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41364</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E81" s="3">
         <v>47800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>49800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>40600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>38600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>28400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>53300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E83" s="3">
         <v>99400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>88100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>85400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>69700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>78300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>30900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>31600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>36600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>31200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>37600</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>204700</v>
+        <v>151200</v>
       </c>
       <c r="E89" s="3">
+        <v>210600</v>
+      </c>
+      <c r="F89" s="3">
         <v>125000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>130500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>115000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>121800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>80200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>39700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>29000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>57900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>32400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>79500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>68600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>48600</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-194700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-153600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-82400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-88900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-91900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-121100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-170200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-42900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-24400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-24100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-24600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-190900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-185400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-72000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-78400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-88500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-123900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-167500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>119900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-34900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-49300</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,53 +4454,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E96" s="3">
         <v>7600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>5700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1700</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,68 +4643,74 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-73300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>95700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-34900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-37900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-27100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-189700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-34400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1200</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="E101" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>8</v>
@@ -4476,8 +4724,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4491,52 +4739,58 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E102" s="3">
         <v>14700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>38800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>30000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>23600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>9700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>500</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NOA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NOA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>NOA</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>936700</v>
+      </c>
+      <c r="E8" s="3">
         <v>810200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>730500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>568600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>516900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>391200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>554400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>233300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>155000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>211200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>370400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>362200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>410000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>515300</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>548400</v>
+        <v>659900</v>
       </c>
       <c r="E9" s="3">
+        <v>535700</v>
+      </c>
+      <c r="F9" s="3">
         <v>513800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>405400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>370000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>268900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>401700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>207100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>166000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>131500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>187300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>330000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>327000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>384500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>490700</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>261800</v>
+        <v>276800</v>
       </c>
       <c r="E10" s="3">
+        <v>274500</v>
+      </c>
+      <c r="F10" s="3">
         <v>216700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>163200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>146900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>122300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>152700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>93400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>67300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>40400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>35200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>25500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>24600</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,8 +900,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,105 +999,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E14" s="3">
         <v>37500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-10500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-21500</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>5000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>115800</v>
+        <v>159900</v>
       </c>
       <c r="E15" s="3">
+        <v>129500</v>
+      </c>
+      <c r="F15" s="3">
         <v>99400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>88100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>85400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>69700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>78900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>43100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>35100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3300</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>703100</v>
+        <v>856400</v>
       </c>
       <c r="E17" s="3">
+        <v>703200</v>
+      </c>
+      <c r="F17" s="3">
         <v>656300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>515500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>483900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>360000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>509100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>278700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>221300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>152100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>209500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>361300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>369200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>422000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>526600</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E18" s="3">
         <v>107100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>74200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>53000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>33000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>31200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>45300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>21900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-11400</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,248 +1245,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-13400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-23700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-28000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-19400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-9400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-14000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>236300</v>
+        <v>225000</v>
       </c>
       <c r="E21" s="3">
+        <v>250000</v>
+      </c>
+      <c r="F21" s="3">
         <v>197300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>169100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>137800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>110300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>126300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>64900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>47100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>35000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>32900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>45400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>28900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12400</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E22" s="3">
         <v>41200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>18100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16900</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1200</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E23" s="3">
         <v>41700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>65100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>62400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>48000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>47500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>30800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-26600</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E24" s="3">
         <v>11100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>17300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-4700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-7100</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E26" s="3">
         <v>30600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>47800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>49800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>40600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>38600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>28600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-19500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E27" s="3">
         <v>30600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>47800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>49800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>40600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>38600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>28400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1681,20 +1741,23 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>67200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>20200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>3200</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E32" s="3">
         <v>13400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>23700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>28000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>19400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>9400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>15900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>14000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E33" s="3">
         <v>30600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>47800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>49800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>40600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>38600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>28400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>53300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16300</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E35" s="3">
         <v>30600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>47800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>49800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>40600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>38600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>28400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>53300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16300</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,56 +2159,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E41" s="3">
         <v>54100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>67100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>51100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>34100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1100</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2167,229 +2256,244 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>1200</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>130800</v>
+      </c>
+      <c r="E43" s="3">
         <v>118300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>100600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>73600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>62100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>33900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>66300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>68200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>54500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>40700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>31800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>138700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>78800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>117900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>231200</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>51500</v>
+        <v>55200</v>
       </c>
       <c r="E44" s="3">
+        <v>48000</v>
+      </c>
+      <c r="F44" s="3">
         <v>49200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>36900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>35200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>15000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>16700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>29400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>145800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9600</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>229700</v>
+        <v>264200</v>
       </c>
       <c r="E46" s="3">
+        <v>226200</v>
+      </c>
+      <c r="F46" s="3">
         <v>223500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>170200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>116300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>93600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>90800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>95100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>70900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>54500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>59400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>118000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>98400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>268500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>251200</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E47" s="3">
         <v>58900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>61700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>55900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>44200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>36300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>33100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8600</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
@@ -2406,108 +2510,117 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>875200</v>
+        <v>998900</v>
       </c>
       <c r="E48" s="3">
+        <v>878900</v>
+      </c>
+      <c r="F48" s="3">
         <v>875100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>488100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>518200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>510400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>470000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>387100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>222200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>179300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>388600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>204800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>194000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>210200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>245000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E49" s="3">
         <v>7200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>300</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3400</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
       <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
         <v>6500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>35200</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>300</v>
+      </c>
+      <c r="E52" s="3">
         <v>3000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>19700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>32100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>50600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>46200</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1177500</v>
+        <v>1327200</v>
       </c>
       <c r="E54" s="3">
+        <v>1177700</v>
+      </c>
+      <c r="F54" s="3">
         <v>1171000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>723700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>686900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>658500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>611100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>505500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>305900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>254500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>270400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>358400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>343100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>496800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>576200</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,296 +2915,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E57" s="3">
         <v>77000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>110700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>75800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>60300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>68000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>46500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>28100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>21500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>45600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>37300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>55500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>131500</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>129200</v>
+      </c>
+      <c r="E58" s="3">
         <v>65500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>71500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>32900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>38000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>37000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>39700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>45600</v>
-      </c>
-      <c r="K58" s="3">
-        <v>23400</v>
       </c>
       <c r="L58" s="3">
         <v>23400</v>
       </c>
       <c r="M58" s="3">
+        <v>23400</v>
+      </c>
+      <c r="N58" s="3">
         <v>22500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>17400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>16100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>22100</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E59" s="3">
         <v>45000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>39200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>23100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>72300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>53000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>219500</v>
+        <v>299700</v>
       </c>
       <c r="E60" s="3">
+        <v>219600</v>
+      </c>
+      <c r="F60" s="3">
         <v>245400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>142100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>127300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>85900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>121300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>109100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>61900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>53800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>46700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>74800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>72000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>143900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>195600</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>553900</v>
+      </c>
+      <c r="E61" s="3">
         <v>507900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>471500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>288800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>274300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>312400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>291600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>234700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>86000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>49900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>60400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>83300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>79500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>218800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>230500</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E62" s="3">
         <v>79400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>89500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>35300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>34400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>51500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>43900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>37700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>51900</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>907200</v>
+        <v>994200</v>
       </c>
       <c r="E66" s="3">
+        <v>907300</v>
+      </c>
+      <c r="F66" s="3">
         <v>901000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>497700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>466900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>463500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>472300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>395400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>189600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>139000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>141600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>209600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>195400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>400500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>478000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>108500</v>
+        <v>128700</v>
       </c>
       <c r="E72" s="3">
+        <v>108600</v>
+      </c>
+      <c r="F72" s="3">
         <v>93200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>52100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-27600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-61600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-83500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-101400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-94700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-95700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-92200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-87300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-141000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-142800</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>270300</v>
+        <v>333000</v>
       </c>
       <c r="E76" s="3">
+        <v>270400</v>
+      </c>
+      <c r="F76" s="3">
         <v>270100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>226000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>220000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>195000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>138900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>109700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>116400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>115600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>128900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>148800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>147700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>96300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>98200</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E81" s="3">
         <v>30600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>47800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>49800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>40600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>38600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>28400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>53300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16300</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>115800</v>
+        <v>158400</v>
       </c>
       <c r="E83" s="3">
+        <v>128600</v>
+      </c>
+      <c r="F83" s="3">
         <v>99400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>88100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>85400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>69700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>78300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>42800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>31600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>36600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>31200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>37600</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>151200</v>
+        <v>192600</v>
       </c>
       <c r="E89" s="3">
+        <v>167600</v>
+      </c>
+      <c r="F89" s="3">
         <v>210600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>125000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>130500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>115000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>121800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>80200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>39700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>29000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>57900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>32400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>79500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>68600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>48600</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-194700</v>
+        <v>-205000</v>
       </c>
       <c r="E91" s="3">
+        <v>-211100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-153600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-82400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-88900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-91900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-121100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-170200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-42900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-24400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-27600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-24100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-40700</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-190900</v>
+        <v>-193100</v>
       </c>
       <c r="E94" s="3">
+        <v>-207300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-185400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-72000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-78400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-88500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-123900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-167500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>119900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-34900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-49300</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,56 +4687,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E96" s="3">
         <v>7400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>7600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>5700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1700</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,74 +4888,80 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E100" s="3">
         <v>32000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-73300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>95700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-17200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-34900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-37900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-27100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-189700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-34400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1200</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>8</v>
@@ -4727,8 +4975,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4742,55 +4990,61 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>14700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>38800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>30000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>23600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>500</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
